--- a/测试数据.xlsx
+++ b/测试数据.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="135">
   <si>
     <t>x2</t>
   </si>
@@ -191,6 +191,12 @@
     <t>bisenetvl_blueface repghostnet 080</t>
   </si>
   <si>
+    <t>fastefficientbisenet_swiftformer_xs</t>
+  </si>
+  <si>
+    <t>fastefficientbisenet_shvit_s3</t>
+  </si>
+  <si>
     <t>3070/FP32</t>
   </si>
   <si>
@@ -317,7 +323,7 @@
     <t>512x512</t>
   </si>
   <si>
-    <t>2.14/2.34/2.29</t>
+    <t>2.14/2.34/2.29/2.24</t>
   </si>
   <si>
     <t>bisenetv1_efficientnet_b3</t>
@@ -585,12 +591,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -607,6 +625,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -715,12 +739,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -909,10 +927,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -921,73 +939,73 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -996,78 +1014,88 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1390,7 +1418,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L50"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="44.6666666666667" customWidth="1"/>
@@ -1488,7 +1516,7 @@
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="14" t="s">
         <v>9</v>
       </c>
       <c r="B5">
@@ -1513,13 +1541,13 @@
       <c r="I5">
         <v>49</v>
       </c>
-      <c r="J5" s="10">
+      <c r="J5" s="13">
         <v>0.772044</v>
       </c>
-      <c r="K5" s="10">
+      <c r="K5" s="13">
         <v>0.881188</v>
       </c>
-      <c r="L5" s="10">
+      <c r="L5" s="13">
         <v>0.856513</v>
       </c>
     </row>
@@ -1637,7 +1665,7 @@
         <v>0.848517</v>
       </c>
     </row>
-    <row r="12" s="10" customFormat="1" spans="1:12">
+    <row r="12" s="13" customFormat="1" spans="1:12">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -1680,26 +1708,26 @@
       </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="6">
         <v>0.754777</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="6">
         <v>0.863089</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="6">
         <v>0.850826</v>
       </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="13" t="s">
         <v>19</v>
       </c>
       <c r="B15">
@@ -1739,7 +1767,7 @@
       </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="14" t="s">
         <v>21</v>
       </c>
       <c r="B17">
@@ -1765,7 +1793,7 @@
       </c>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="14" t="s">
         <v>22</v>
       </c>
       <c r="B18">
@@ -1800,7 +1828,7 @@
       </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="14" t="s">
         <v>23</v>
       </c>
       <c r="B19">
@@ -1840,7 +1868,7 @@
       </c>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="14" t="s">
         <v>25</v>
       </c>
       <c r="B21">
@@ -1875,7 +1903,7 @@
       </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="14" t="s">
         <v>26</v>
       </c>
       <c r="B22">
@@ -1892,29 +1920,29 @@
       </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="10">
         <v>0.744506</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="10">
         <v>0.860528</v>
       </c>
-      <c r="D23" s="7">
+      <c r="D23" s="10">
         <v>0.839851</v>
       </c>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7">
+      <c r="E23" s="10"/>
+      <c r="F23" s="10">
         <v>0.751574</v>
       </c>
-      <c r="G23" s="7">
+      <c r="G23" s="10">
         <v>0.868257</v>
       </c>
-      <c r="H23" s="7">
+      <c r="H23" s="10">
         <v>0.841741</v>
       </c>
-      <c r="I23" s="7">
+      <c r="I23" s="10">
         <v>57.3</v>
       </c>
     </row>
@@ -1947,7 +1975,7 @@
       </c>
     </row>
     <row r="26" spans="1:12">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="14" t="s">
         <v>30</v>
       </c>
       <c r="B26">
@@ -1996,7 +2024,7 @@
       </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="10" t="s">
+      <c r="A28" s="13" t="s">
         <v>32</v>
       </c>
       <c r="B28">
@@ -2036,7 +2064,7 @@
       </c>
     </row>
     <row r="30" spans="1:12">
-      <c r="A30" s="11" t="s">
+      <c r="A30" s="14" t="s">
         <v>34</v>
       </c>
       <c r="B30">
@@ -2061,8 +2089,8 @@
         <v>0.854449</v>
       </c>
     </row>
-    <row r="31" spans="1:9">
-      <c r="A31" s="11" t="s">
+    <row r="31" spans="1:13">
+      <c r="A31" s="15" t="s">
         <v>35</v>
       </c>
       <c r="B31">
@@ -2083,8 +2111,11 @@
       <c r="H31">
         <v>0.843659</v>
       </c>
-      <c r="I31" s="12" t="s">
+      <c r="I31" s="16" t="s">
         <v>36</v>
+      </c>
+      <c r="M31">
+        <v>30.6</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2119,7 +2150,7 @@
       </c>
     </row>
     <row r="34" spans="1:12">
-      <c r="A34" s="11" t="s">
+      <c r="A34" s="14" t="s">
         <v>39</v>
       </c>
       <c r="B34">
@@ -2263,7 +2294,7 @@
       </c>
     </row>
     <row r="43" spans="1:12">
-      <c r="A43" s="11" t="s">
+      <c r="A43" s="14" t="s">
         <v>48</v>
       </c>
       <c r="B43">
@@ -2331,7 +2362,7 @@
       </c>
     </row>
     <row r="47" spans="1:12">
-      <c r="A47" s="11" t="s">
+      <c r="A47" s="14" t="s">
         <v>52</v>
       </c>
       <c r="B47">
@@ -2357,7 +2388,7 @@
       </c>
     </row>
     <row r="48" spans="1:12">
-      <c r="A48" s="11" t="s">
+      <c r="A48" s="14" t="s">
         <v>53</v>
       </c>
       <c r="B48">
@@ -2392,7 +2423,7 @@
       </c>
     </row>
     <row r="49" spans="1:12">
-      <c r="A49" s="11" t="s">
+      <c r="A49" s="14" t="s">
         <v>54</v>
       </c>
       <c r="B49">
@@ -2438,6 +2469,58 @@
       </c>
       <c r="H50">
         <v>0.771671</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12">
+      <c r="A51" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="B51">
+        <v>0.734976</v>
+      </c>
+      <c r="C51">
+        <v>0.863216</v>
+      </c>
+      <c r="D51">
+        <v>0.824038</v>
+      </c>
+      <c r="I51">
+        <v>22.9</v>
+      </c>
+      <c r="J51">
+        <v>0.745505</v>
+      </c>
+      <c r="K51">
+        <v>0.860679</v>
+      </c>
+      <c r="L51">
+        <v>0.84022</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12">
+      <c r="A52" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="B52">
+        <v>0.721233</v>
+      </c>
+      <c r="C52">
+        <v>0.857926</v>
+      </c>
+      <c r="D52">
+        <v>0.810198</v>
+      </c>
+      <c r="I52">
+        <v>11.42</v>
+      </c>
+      <c r="J52">
+        <v>0.734794</v>
+      </c>
+      <c r="K52">
+        <v>0.857295</v>
+      </c>
+      <c r="L52">
+        <v>0.830844</v>
       </c>
     </row>
   </sheetData>
@@ -2468,7 +2551,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -2484,18 +2567,18 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B2">
         <v>0.7731</v>
@@ -2514,8 +2597,8 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="5" t="s">
-        <v>60</v>
+      <c r="A3" s="8" t="s">
+        <v>62</v>
       </c>
       <c r="B3">
         <v>0.76</v>
@@ -2528,8 +2611,8 @@
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="4" t="s">
-        <v>61</v>
+      <c r="A4" s="7" t="s">
+        <v>63</v>
       </c>
       <c r="B4">
         <v>0.7558</v>
@@ -2545,32 +2628,32 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="10">
         <v>0.744506</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="10">
         <v>0.860528</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="10">
         <v>0.839851</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="10">
         <v>57.3</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="10">
         <v>7.56</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="10">
         <v>4.11</v>
       </c>
-      <c r="H5" s="7"/>
+      <c r="H5" s="10"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="5" t="s">
-        <v>62</v>
+      <c r="A6" s="8" t="s">
+        <v>64</v>
       </c>
       <c r="B6">
         <v>0.7432</v>
@@ -2587,7 +2670,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B7">
         <v>0.7426</v>
@@ -2601,7 +2684,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B8">
         <v>0.742</v>
@@ -2617,8 +2700,8 @@
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="5" t="s">
-        <v>65</v>
+      <c r="A9" s="8" t="s">
+        <v>67</v>
       </c>
       <c r="B9">
         <v>0.7406</v>
@@ -2633,12 +2716,12 @@
         <v>2.64</v>
       </c>
       <c r="J9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="5" t="s">
-        <v>67</v>
+      <c r="A10" s="8" t="s">
+        <v>69</v>
       </c>
       <c r="B10">
         <v>0.7379</v>
@@ -2656,9 +2739,9 @@
         <v>0.8666</v>
       </c>
     </row>
-    <row r="11" s="3" customFormat="1" spans="1:9">
-      <c r="A11" s="5" t="s">
-        <v>68</v>
+    <row r="11" s="6" customFormat="1" spans="1:9">
+      <c r="A11" s="8" t="s">
+        <v>70</v>
       </c>
       <c r="B11">
         <v>0.7358</v>
@@ -2678,8 +2761,8 @@
       <c r="I11"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="4" t="s">
-        <v>69</v>
+      <c r="A12" s="7" t="s">
+        <v>71</v>
       </c>
       <c r="B12">
         <v>0.7308</v>
@@ -2696,7 +2779,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B13">
         <v>0.7294</v>
@@ -2709,29 +2792,29 @@
       </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B14" s="3">
+      <c r="A14" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" s="6">
         <v>0.7271</v>
       </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3">
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6">
         <v>8.9</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="6">
         <v>1.81</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="6">
         <v>1</v>
       </c>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="4" t="s">
-        <v>72</v>
+      <c r="A15" s="7" t="s">
+        <v>74</v>
       </c>
       <c r="B15">
         <v>0.726864</v>
@@ -2753,32 +2836,32 @@
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="B16" s="9">
+      <c r="A16" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B16" s="12">
         <v>0.722361</v>
       </c>
-      <c r="C16" s="9">
+      <c r="C16" s="12">
         <v>0.867663</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="12">
         <v>0.803904</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="12">
         <v>17.4</v>
       </c>
-      <c r="F16" s="9">
+      <c r="F16" s="12">
         <v>2.29</v>
       </c>
-      <c r="G16" s="9">
+      <c r="G16" s="12">
         <v>1.41</v>
       </c>
-      <c r="H16" s="9"/>
+      <c r="H16" s="12"/>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B17">
         <v>0.7215</v>
@@ -2790,9 +2873,9 @@
         <v>2.09</v>
       </c>
     </row>
-    <row r="18" s="3" customFormat="1" ht="12" customHeight="1" spans="1:9">
-      <c r="A18" s="5" t="s">
-        <v>75</v>
+    <row r="18" s="6" customFormat="1" ht="12" customHeight="1" spans="1:9">
+      <c r="A18" s="8" t="s">
+        <v>77</v>
       </c>
       <c r="B18">
         <v>0.7161</v>
@@ -2813,7 +2896,7 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B19">
         <v>0.7138</v>
@@ -2826,8 +2909,8 @@
       </c>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="4" t="s">
-        <v>77</v>
+      <c r="A20" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="B20">
         <v>0.710494</v>
@@ -2850,7 +2933,7 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B21">
         <v>0.7101</v>
@@ -2863,8 +2946,8 @@
       </c>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="5" t="s">
-        <v>79</v>
+      <c r="A22" s="8" t="s">
+        <v>81</v>
       </c>
       <c r="B22">
         <v>0.71</v>
@@ -2880,8 +2963,8 @@
       </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="5" t="s">
-        <v>80</v>
+      <c r="A23" s="8" t="s">
+        <v>82</v>
       </c>
       <c r="B23">
         <v>0.7089</v>
@@ -2895,11 +2978,11 @@
       <c r="G23">
         <v>0.94</v>
       </c>
-      <c r="I23" s="3"/>
-    </row>
-    <row r="24" s="3" customFormat="1" spans="1:10">
+      <c r="I23" s="6"/>
+    </row>
+    <row r="24" s="6" customFormat="1" spans="1:10">
       <c r="A24" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B24">
         <v>0.707672</v>
@@ -2918,8 +3001,8 @@
       <c r="J24"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="4" t="s">
-        <v>82</v>
+      <c r="A25" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="B25">
         <v>0.707574</v>
@@ -2942,7 +3025,7 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B26">
         <v>0.7066</v>
@@ -2955,8 +3038,8 @@
       </c>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="4" t="s">
-        <v>84</v>
+      <c r="A27" s="7" t="s">
+        <v>86</v>
       </c>
       <c r="B27">
         <v>0.698648</v>
@@ -2976,31 +3059,31 @@
       <c r="G27">
         <v>1.64</v>
       </c>
-      <c r="J27" s="3"/>
+      <c r="J27" s="6"/>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="B28" s="3">
+      <c r="A28" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28" s="6">
         <v>0.683513</v>
       </c>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3">
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6">
         <v>10.4</v>
       </c>
-      <c r="F28" s="3">
+      <c r="F28" s="6">
         <v>1.72</v>
       </c>
-      <c r="G28" s="3">
+      <c r="G28" s="6">
         <v>1.33</v>
       </c>
-      <c r="H28" s="3"/>
+      <c r="H28" s="6"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="4" t="s">
-        <v>86</v>
+      <c r="A29" s="7" t="s">
+        <v>88</v>
       </c>
       <c r="B29">
         <v>0.683125</v>
@@ -3023,7 +3106,7 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B30">
         <v>0.6737</v>
@@ -3036,8 +3119,8 @@
       </c>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="4" t="s">
-        <v>88</v>
+      <c r="A31" s="7" t="s">
+        <v>90</v>
       </c>
       <c r="B31">
         <v>0.673307</v>
@@ -3059,29 +3142,29 @@
       </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="B32" s="3">
+      <c r="A32" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B32" s="6">
         <v>0.667316</v>
       </c>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3">
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6">
         <v>4.9</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="6">
         <v>0.8</v>
       </c>
-      <c r="G32" s="3">
+      <c r="G32" s="6">
         <v>0.67</v>
       </c>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="4" t="s">
-        <v>90</v>
+      <c r="A33" s="7" t="s">
+        <v>92</v>
       </c>
       <c r="B33">
         <v>0.660027</v>
@@ -3103,8 +3186,8 @@
       </c>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="4" t="s">
-        <v>91</v>
+      <c r="A34" s="7" t="s">
+        <v>93</v>
       </c>
       <c r="B34">
         <v>0.65747</v>
@@ -3126,28 +3209,28 @@
       </c>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="B35" s="9">
+      <c r="A35" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="B35" s="12">
         <v>0</v>
       </c>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9">
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12">
         <v>4.3</v>
       </c>
-      <c r="F35" s="9">
+      <c r="F35" s="12">
         <v>0.78</v>
       </c>
-      <c r="G35" s="9">
+      <c r="G35" s="12">
         <v>0.65</v>
       </c>
-      <c r="H35" s="9"/>
+      <c r="H35" s="12"/>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B36">
         <v>0.712137</v>
@@ -3164,7 +3247,7 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B37">
         <v>0.715039</v>
@@ -3201,21 +3284,21 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3227,7 +3310,7 @@
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B4" s="1">
@@ -3236,118 +3319,118 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B5" s="1">
         <v>4.53</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="1">
+        <v>4.42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B7" s="1">
         <v>3.4</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B7" s="1">
+    <row r="8" spans="1:2">
+      <c r="A8" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B8" s="1">
         <v>2.92</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B8" s="1">
-        <v>2.52</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B9" s="1">
+        <v>2.52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B10" s="1">
         <v>2.35</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="1" t="s">
+    <row r="11" spans="1:2">
+      <c r="A11" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B11" s="1">
         <v>2.22</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="1" t="s">
+    <row r="12" spans="1:2">
+      <c r="A12" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B12" s="1">
         <v>2.02</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B12" s="1">
+    <row r="13" spans="1:2">
+      <c r="A13" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B13" s="1">
         <v>1.81</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B13" s="1">
-        <v>1.6</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="B14" s="1">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B15" s="1">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="B16" s="1">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="B17" s="1">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B18" s="1">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="4" t="s">
         <v>54</v>
       </c>
       <c r="B19" s="1">
@@ -3355,43 +3438,43 @@
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="1" t="s">
-        <v>22</v>
+      <c r="A20" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="B20" s="1">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B21" s="1">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="1">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B23" s="1">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B24" s="1">
         <v>1.19</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B23" s="1">
-        <v>1.14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B24" s="1">
-        <v>1.07</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -3399,40 +3482,48 @@
         <v>109</v>
       </c>
       <c r="B25" s="1">
-        <v>0.989</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="B26" s="1">
-        <v>0.98</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B27" s="1">
+        <v>0.989</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B28" s="1">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B27" s="1">
+      <c r="B29" s="1">
         <v>0.89</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
-      <c r="A28" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B28" s="1">
+    <row r="30" spans="1:2">
+      <c r="A30" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B30" s="1">
         <v>0.799</v>
       </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1"/>
@@ -3451,8 +3542,8 @@
       <c r="B34" s="1"/>
     </row>
   </sheetData>
-  <sortState ref="A2:B28">
-    <sortCondition ref="B2:B28" descending="1"/>
+  <sortState ref="A2:B30">
+    <sortCondition ref="B2:B30" descending="1"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -3471,15 +3562,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B2">
         <v>1.12</v>
@@ -3487,7 +3578,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -3495,7 +3586,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B4">
         <v>3.26</v>
@@ -3503,7 +3594,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B5">
         <v>4.6</v>
@@ -3511,7 +3602,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B6">
         <v>3.26</v>
@@ -3519,7 +3610,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B7">
         <v>0.49</v>
@@ -3527,7 +3618,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B8">
         <v>4.2</v>
@@ -3535,7 +3626,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B9">
         <v>1.74</v>
@@ -3543,7 +3634,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B10">
         <v>1.14</v>
@@ -3568,18 +3659,18 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B2" s="1">
         <v>2.7</v>
@@ -3590,7 +3681,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B3" s="1">
         <v>2.47</v>
@@ -3598,7 +3689,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B4" s="1">
         <v>2.12</v>
@@ -3606,7 +3697,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B5" s="1">
         <v>2.06</v>
@@ -3614,7 +3705,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B6" s="1">
         <v>1.37</v>
@@ -3622,7 +3713,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B7" s="1">
         <v>1.26</v>
@@ -3630,7 +3721,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B8" s="1">
         <v>0.83</v>
@@ -3638,7 +3729,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B9" s="1">
         <v>0.69</v>
@@ -3646,7 +3737,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B10" s="1">
         <v>0.58</v>
@@ -3654,7 +3745,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B11" s="1">
         <v>0.45</v>

--- a/测试数据.xlsx
+++ b/测试数据.xlsx
@@ -433,10 +433,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -448,7 +448,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="0"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -456,6 +456,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -469,22 +477,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -495,6 +504,14 @@
       <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -514,9 +531,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -525,14 +548,6 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -556,7 +571,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -568,41 +590,13 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="38">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -636,7 +630,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -648,7 +642,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -660,7 +666,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -678,7 +708,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -690,43 +720,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -738,7 +732,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -756,19 +750,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -780,37 +798,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -821,6 +815,47 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -839,17 +874,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -873,30 +902,6 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
@@ -910,166 +915,155 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1078,27 +1072,18 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1516,7 +1501,7 @@
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="12" t="s">
         <v>9</v>
       </c>
       <c r="B5">
@@ -1528,7 +1513,6 @@
       <c r="D5">
         <v>0.850913</v>
       </c>
-      <c r="E5"/>
       <c r="F5">
         <v>0.768479</v>
       </c>
@@ -1541,13 +1525,13 @@
       <c r="I5">
         <v>49</v>
       </c>
-      <c r="J5" s="13">
+      <c r="J5" s="11">
         <v>0.772044</v>
       </c>
-      <c r="K5" s="13">
+      <c r="K5" s="11">
         <v>0.881188</v>
       </c>
-      <c r="L5" s="13">
+      <c r="L5" s="11">
         <v>0.856513</v>
       </c>
     </row>
@@ -1665,7 +1649,7 @@
         <v>0.848517</v>
       </c>
     </row>
-    <row r="12" s="13" customFormat="1" spans="1:12">
+    <row r="12" s="11" customFormat="1" spans="1:12">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -1708,26 +1692,26 @@
       </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="4">
         <v>0.754777</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="4">
         <v>0.863089</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="4">
         <v>0.850826</v>
       </c>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="11" t="s">
         <v>19</v>
       </c>
       <c r="B15">
@@ -1767,7 +1751,7 @@
       </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="12" t="s">
         <v>21</v>
       </c>
       <c r="B17">
@@ -1793,7 +1777,7 @@
       </c>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="12" t="s">
         <v>22</v>
       </c>
       <c r="B18">
@@ -1828,7 +1812,7 @@
       </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="12" t="s">
         <v>23</v>
       </c>
       <c r="B19">
@@ -1868,7 +1852,7 @@
       </c>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="12" t="s">
         <v>25</v>
       </c>
       <c r="B21">
@@ -1903,7 +1887,7 @@
       </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="12" t="s">
         <v>26</v>
       </c>
       <c r="B22">
@@ -1920,29 +1904,29 @@
       </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="10">
+      <c r="B23" s="8">
         <v>0.744506</v>
       </c>
-      <c r="C23" s="10">
+      <c r="C23" s="8">
         <v>0.860528</v>
       </c>
-      <c r="D23" s="10">
+      <c r="D23" s="8">
         <v>0.839851</v>
       </c>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10">
+      <c r="E23" s="8"/>
+      <c r="F23" s="8">
         <v>0.751574</v>
       </c>
-      <c r="G23" s="10">
+      <c r="G23" s="8">
         <v>0.868257</v>
       </c>
-      <c r="H23" s="10">
+      <c r="H23" s="8">
         <v>0.841741</v>
       </c>
-      <c r="I23" s="10">
+      <c r="I23" s="8">
         <v>57.3</v>
       </c>
     </row>
@@ -1975,7 +1959,7 @@
       </c>
     </row>
     <row r="26" spans="1:12">
-      <c r="A26" s="14" t="s">
+      <c r="A26" s="12" t="s">
         <v>30</v>
       </c>
       <c r="B26">
@@ -2024,7 +2008,7 @@
       </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="13" t="s">
+      <c r="A28" s="11" t="s">
         <v>32</v>
       </c>
       <c r="B28">
@@ -2064,7 +2048,7 @@
       </c>
     </row>
     <row r="30" spans="1:12">
-      <c r="A30" s="14" t="s">
+      <c r="A30" s="12" t="s">
         <v>34</v>
       </c>
       <c r="B30">
@@ -2090,7 +2074,7 @@
       </c>
     </row>
     <row r="31" spans="1:13">
-      <c r="A31" s="15" t="s">
+      <c r="A31" s="13" t="s">
         <v>35</v>
       </c>
       <c r="B31">
@@ -2111,7 +2095,7 @@
       <c r="H31">
         <v>0.843659</v>
       </c>
-      <c r="I31" s="16" t="s">
+      <c r="I31" s="1" t="s">
         <v>36</v>
       </c>
       <c r="M31">
@@ -2150,7 +2134,7 @@
       </c>
     </row>
     <row r="34" spans="1:12">
-      <c r="A34" s="14" t="s">
+      <c r="A34" s="12" t="s">
         <v>39</v>
       </c>
       <c r="B34">
@@ -2294,7 +2278,7 @@
       </c>
     </row>
     <row r="43" spans="1:12">
-      <c r="A43" s="14" t="s">
+      <c r="A43" s="12" t="s">
         <v>48</v>
       </c>
       <c r="B43">
@@ -2362,7 +2346,7 @@
       </c>
     </row>
     <row r="47" spans="1:12">
-      <c r="A47" s="14" t="s">
+      <c r="A47" s="12" t="s">
         <v>52</v>
       </c>
       <c r="B47">
@@ -2388,7 +2372,7 @@
       </c>
     </row>
     <row r="48" spans="1:12">
-      <c r="A48" s="14" t="s">
+      <c r="A48" s="12" t="s">
         <v>53</v>
       </c>
       <c r="B48">
@@ -2423,7 +2407,7 @@
       </c>
     </row>
     <row r="49" spans="1:12">
-      <c r="A49" s="14" t="s">
+      <c r="A49" s="12" t="s">
         <v>54</v>
       </c>
       <c r="B49">
@@ -2472,7 +2456,7 @@
       </c>
     </row>
     <row r="51" spans="1:12">
-      <c r="A51" s="14" t="s">
+      <c r="A51" s="12" t="s">
         <v>56</v>
       </c>
       <c r="B51">
@@ -2498,7 +2482,7 @@
       </c>
     </row>
     <row r="52" spans="1:12">
-      <c r="A52" s="14" t="s">
+      <c r="A52" s="12" t="s">
         <v>57</v>
       </c>
       <c r="B52">
@@ -2551,7 +2535,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -2597,7 +2581,7 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B3">
@@ -2611,7 +2595,7 @@
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="5" t="s">
         <v>63</v>
       </c>
       <c r="B4">
@@ -2628,31 +2612,31 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="8">
         <v>0.744506</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="8">
         <v>0.860528</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="8">
         <v>0.839851</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="8">
         <v>57.3</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="8">
         <v>7.56</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="8">
         <v>4.11</v>
       </c>
-      <c r="H5" s="10"/>
+      <c r="H5" s="8"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="6" t="s">
         <v>64</v>
       </c>
       <c r="B6">
@@ -2700,7 +2684,7 @@
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>67</v>
       </c>
       <c r="B9">
@@ -2720,7 +2704,7 @@
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="6" t="s">
         <v>69</v>
       </c>
       <c r="B10">
@@ -2739,8 +2723,8 @@
         <v>0.8666</v>
       </c>
     </row>
-    <row r="11" s="6" customFormat="1" spans="1:9">
-      <c r="A11" s="8" t="s">
+    <row r="11" s="4" customFormat="1" spans="1:9">
+      <c r="A11" s="6" t="s">
         <v>70</v>
       </c>
       <c r="B11">
@@ -2761,7 +2745,7 @@
       <c r="I11"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="5" t="s">
         <v>71</v>
       </c>
       <c r="B12">
@@ -2792,28 +2776,28 @@
       </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="4">
         <v>0.7271</v>
       </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6">
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4">
         <v>8.9</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="4">
         <v>1.81</v>
       </c>
-      <c r="G14" s="6">
+      <c r="G14" s="4">
         <v>1</v>
       </c>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="5" t="s">
         <v>74</v>
       </c>
       <c r="B15">
@@ -2836,28 +2820,28 @@
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="10">
         <v>0.722361</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="10">
         <v>0.867663</v>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="10">
         <v>0.803904</v>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="10">
         <v>17.4</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="10">
         <v>2.29</v>
       </c>
-      <c r="G16" s="12">
+      <c r="G16" s="10">
         <v>1.41</v>
       </c>
-      <c r="H16" s="12"/>
+      <c r="H16" s="10"/>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
@@ -2873,8 +2857,8 @@
         <v>2.09</v>
       </c>
     </row>
-    <row r="18" s="6" customFormat="1" ht="12" customHeight="1" spans="1:9">
-      <c r="A18" s="8" t="s">
+    <row r="18" s="4" customFormat="1" ht="12" customHeight="1" spans="1:9">
+      <c r="A18" s="6" t="s">
         <v>77</v>
       </c>
       <c r="B18">
@@ -2909,7 +2893,7 @@
       </c>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="5" t="s">
         <v>79</v>
       </c>
       <c r="B20">
@@ -2946,7 +2930,7 @@
       </c>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="6" t="s">
         <v>81</v>
       </c>
       <c r="B22">
@@ -2963,7 +2947,7 @@
       </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="6" t="s">
         <v>82</v>
       </c>
       <c r="B23">
@@ -2978,9 +2962,9 @@
       <c r="G23">
         <v>0.94</v>
       </c>
-      <c r="I23" s="6"/>
-    </row>
-    <row r="24" s="6" customFormat="1" spans="1:10">
+      <c r="I23" s="4"/>
+    </row>
+    <row r="24" s="4" customFormat="1" spans="1:10">
       <c r="A24" t="s">
         <v>83</v>
       </c>
@@ -3001,7 +2985,7 @@
       <c r="J24"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="5" t="s">
         <v>84</v>
       </c>
       <c r="B25">
@@ -3038,7 +3022,7 @@
       </c>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="5" t="s">
         <v>86</v>
       </c>
       <c r="B27">
@@ -3059,30 +3043,30 @@
       <c r="G27">
         <v>1.64</v>
       </c>
-      <c r="J27" s="6"/>
+      <c r="J27" s="4"/>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="6">
+      <c r="B28" s="4">
         <v>0.683513</v>
       </c>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6">
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4">
         <v>10.4</v>
       </c>
-      <c r="F28" s="6">
+      <c r="F28" s="4">
         <v>1.72</v>
       </c>
-      <c r="G28" s="6">
+      <c r="G28" s="4">
         <v>1.33</v>
       </c>
-      <c r="H28" s="6"/>
+      <c r="H28" s="4"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="7" t="s">
+      <c r="A29" s="5" t="s">
         <v>88</v>
       </c>
       <c r="B29">
@@ -3119,7 +3103,7 @@
       </c>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="5" t="s">
         <v>90</v>
       </c>
       <c r="B31">
@@ -3142,28 +3126,28 @@
       </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="B32" s="6">
+      <c r="B32" s="4">
         <v>0.667316</v>
       </c>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6">
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4">
         <v>4.9</v>
       </c>
-      <c r="F32" s="6">
+      <c r="F32" s="4">
         <v>0.8</v>
       </c>
-      <c r="G32" s="6">
+      <c r="G32" s="4">
         <v>0.67</v>
       </c>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="7" t="s">
+      <c r="A33" s="5" t="s">
         <v>92</v>
       </c>
       <c r="B33">
@@ -3186,7 +3170,7 @@
       </c>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="7" t="s">
+      <c r="A34" s="5" t="s">
         <v>93</v>
       </c>
       <c r="B34">
@@ -3209,24 +3193,24 @@
       </c>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="11" t="s">
+      <c r="A35" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="B35" s="12">
+      <c r="B35" s="10">
         <v>0</v>
       </c>
-      <c r="C35" s="12"/>
-      <c r="D35" s="12"/>
-      <c r="E35" s="12">
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10">
         <v>4.3</v>
       </c>
-      <c r="F35" s="12">
+      <c r="F35" s="10">
         <v>0.78</v>
       </c>
-      <c r="G35" s="12">
+      <c r="G35" s="10">
         <v>0.65</v>
       </c>
-      <c r="H35" s="12"/>
+      <c r="H35" s="10"/>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
@@ -3326,7 +3310,7 @@
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>56</v>
       </c>
       <c r="B6" s="1">
@@ -3430,7 +3414,7 @@
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="3" t="s">
         <v>54</v>
       </c>
       <c r="B19" s="1">
@@ -3438,7 +3422,7 @@
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="2" t="s">
         <v>57</v>
       </c>
       <c r="B20" s="1">
@@ -3470,7 +3454,7 @@
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="B24" s="1">

--- a/测试数据.xlsx
+++ b/测试数据.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\F\ABlueFaceProj\20240618\Seg\Beta_BiSeNet-master_Slim\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{781BEED3-F9DC-4C40-8566-B0B5A9AD232D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="22368" windowHeight="9420"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="大模型" sheetId="1" r:id="rId1"/>
@@ -21,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="136">
   <si>
     <t>x2</t>
   </si>
@@ -426,19 +432,17 @@
   </si>
   <si>
     <t>yolov6-nano</t>
+  </si>
+  <si>
+    <t>fastefficientbisenet_inceptionnext_atto_v2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -447,151 +451,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <sz val="9"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="37">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -606,210 +480,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.6"/>
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.8"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.6"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -817,253 +511,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1074,72 +526,23 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1397,27 +800,27 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:M52"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:M53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="44.6666666666667" customWidth="1"/>
-    <col min="2" max="2" width="8.88888888888889" customWidth="1"/>
-    <col min="3" max="3" width="10.8888888888889" customWidth="1"/>
-    <col min="4" max="4" width="10.4444444444444" customWidth="1"/>
-    <col min="6" max="8" width="9.66666666666667"/>
-    <col min="9" max="9" width="11.4444444444444" customWidth="1"/>
-    <col min="10" max="11" width="9.66666666666667"/>
-    <col min="12" max="12" width="15.1851851851852" customWidth="1"/>
-    <col min="13" max="13" width="13.4537037037037" customWidth="1"/>
+    <col min="1" max="1" width="59.109375" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" customWidth="1"/>
+    <col min="3" max="3" width="10.88671875" customWidth="1"/>
+    <col min="4" max="4" width="10.44140625" customWidth="1"/>
+    <col min="6" max="8" width="9.6640625"/>
+    <col min="9" max="9" width="11.44140625" customWidth="1"/>
+    <col min="10" max="11" width="9.6640625"/>
+    <col min="12" max="12" width="15.21875" customWidth="1"/>
+    <col min="13" max="13" width="13.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1434,385 +837,375 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2">
-        <v>0.779897</v>
+        <v>0.77989699999999995</v>
       </c>
       <c r="C2">
-        <v>0.893358</v>
+        <v>0.89335799999999999</v>
       </c>
       <c r="D2">
-        <v>0.855201</v>
+        <v>0.85520099999999999</v>
       </c>
       <c r="F2">
-        <v>0.784612</v>
+        <v>0.78461199999999998</v>
       </c>
       <c r="G2">
-        <v>0.890915</v>
+        <v>0.89091500000000001</v>
       </c>
       <c r="H2">
-        <v>0.862894</v>
+        <v>0.86289400000000005</v>
       </c>
       <c r="I2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
       <c r="B3">
-        <v>0.777614</v>
+        <v>0.77761400000000003</v>
       </c>
       <c r="C3">
-        <v>0.887592</v>
+        <v>0.88759200000000005</v>
       </c>
       <c r="D3">
-        <v>0.857871</v>
+        <v>0.85787100000000005</v>
       </c>
       <c r="F3">
-        <v>0.791345</v>
+        <v>0.79134499999999997</v>
       </c>
       <c r="G3">
-        <v>0.892739</v>
+        <v>0.89273899999999995</v>
       </c>
       <c r="H3">
-        <v>0.869638</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+        <v>0.86963800000000002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
       <c r="B4">
-        <v>0.772429</v>
+        <v>0.77242900000000003</v>
       </c>
       <c r="C4">
-        <v>0.891295</v>
+        <v>0.89129499999999995</v>
       </c>
       <c r="D4">
-        <v>0.849285</v>
+        <v>0.84928499999999996</v>
       </c>
       <c r="I4">
         <v>124</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="12" t="s">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B5">
         <v>0.770065</v>
       </c>
       <c r="C5">
-        <v>0.88428</v>
+        <v>0.88427999999999995</v>
       </c>
       <c r="D5">
-        <v>0.850913</v>
+        <v>0.85091300000000003</v>
       </c>
       <c r="F5">
-        <v>0.768479</v>
+        <v>0.76847900000000002</v>
       </c>
       <c r="G5">
-        <v>0.863736</v>
+        <v>0.86373599999999995</v>
       </c>
       <c r="H5">
-        <v>0.868333</v>
+        <v>0.86833300000000002</v>
       </c>
       <c r="I5">
         <v>49</v>
       </c>
-      <c r="J5" s="11">
-        <v>0.772044</v>
-      </c>
-      <c r="K5" s="11">
-        <v>0.881188</v>
-      </c>
-      <c r="L5" s="11">
-        <v>0.856513</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="J5">
+        <v>0.77204399999999995</v>
+      </c>
+      <c r="K5">
+        <v>0.88118799999999997</v>
+      </c>
+      <c r="L5">
+        <v>0.85651299999999997</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
       <c r="B6">
-        <v>0.767732</v>
+        <v>0.76773199999999997</v>
       </c>
       <c r="C6">
-        <v>0.871419</v>
+        <v>0.87141900000000005</v>
       </c>
       <c r="D6">
-        <v>0.861395</v>
+        <v>0.86139500000000002</v>
       </c>
       <c r="F6">
-        <v>0.77104</v>
+        <v>0.77103999999999995</v>
       </c>
       <c r="G6">
-        <v>0.867631</v>
+        <v>0.86763100000000004</v>
       </c>
       <c r="H6">
-        <v>0.868188</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+        <v>0.86818799999999996</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
       <c r="B7">
-        <v>0.766295</v>
+        <v>0.76629499999999995</v>
       </c>
       <c r="C7">
-        <v>0.885472</v>
+        <v>0.88547200000000004</v>
       </c>
       <c r="D7">
-        <v>0.84466</v>
+        <v>0.84465999999999997</v>
       </c>
       <c r="F7">
-        <v>0.774369</v>
+        <v>0.77436899999999997</v>
       </c>
       <c r="G7">
-        <v>0.893263</v>
+        <v>0.89326300000000003</v>
       </c>
       <c r="H7">
-        <v>0.848467</v>
+        <v>0.84846699999999997</v>
       </c>
       <c r="I7">
         <v>85.6</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
       <c r="B8">
-        <v>0.76426</v>
+        <v>0.76426000000000005</v>
       </c>
       <c r="C8">
-        <v>0.885592</v>
+        <v>0.88559200000000005</v>
       </c>
       <c r="D8">
-        <v>0.842315</v>
+        <v>0.84231500000000004</v>
       </c>
       <c r="I8">
         <v>58.84</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
       <c r="B9">
-        <v>0.762569</v>
+        <v>0.76256900000000005</v>
       </c>
       <c r="C9">
-        <v>0.884121</v>
+        <v>0.88412100000000005</v>
       </c>
       <c r="D9">
-        <v>0.841114</v>
+        <v>0.84111400000000003</v>
       </c>
       <c r="I9">
         <v>115</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>
       <c r="B10">
-        <v>0.76245</v>
+        <v>0.76244999999999996</v>
       </c>
       <c r="C10">
-        <v>0.881312</v>
+        <v>0.88131199999999998</v>
       </c>
       <c r="D10">
-        <v>0.84433</v>
+        <v>0.84433000000000002</v>
       </c>
       <c r="I10">
         <v>113</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>15</v>
       </c>
       <c r="B11">
-        <v>0.760919</v>
+        <v>0.76091900000000001</v>
       </c>
       <c r="C11">
-        <v>0.874303</v>
+        <v>0.87430300000000005</v>
       </c>
       <c r="D11">
-        <v>0.848517</v>
-      </c>
-    </row>
-    <row r="12" s="11" customFormat="1" spans="1:12">
+        <v>0.84851699999999997</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>16</v>
       </c>
       <c r="B12">
-        <v>0.760356</v>
+        <v>0.76035600000000003</v>
       </c>
       <c r="C12">
-        <v>0.884887</v>
+        <v>0.88488699999999998</v>
       </c>
       <c r="D12">
-        <v>0.836608</v>
-      </c>
-      <c r="E12"/>
+        <v>0.83660800000000002</v>
+      </c>
       <c r="F12">
-        <v>0.763411</v>
+        <v>0.76341099999999995</v>
       </c>
       <c r="G12">
-        <v>0.890017</v>
+        <v>0.89001699999999995</v>
       </c>
       <c r="H12">
-        <v>0.837235</v>
-      </c>
-      <c r="I12"/>
-      <c r="J12"/>
-      <c r="K12"/>
-      <c r="L12"/>
-    </row>
-    <row r="13" spans="1:4">
+        <v>0.83723499999999995</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>17</v>
       </c>
       <c r="B13">
-        <v>0.756666</v>
+        <v>0.75666599999999995</v>
       </c>
       <c r="C13">
-        <v>0.883305</v>
+        <v>0.88330500000000001</v>
       </c>
       <c r="D13">
-        <v>0.834607</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="4" t="s">
+        <v>0.83460699999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="4">
-        <v>0.754777</v>
-      </c>
-      <c r="C14" s="4">
+      <c r="B14">
+        <v>0.75477700000000003</v>
+      </c>
+      <c r="C14">
         <v>0.863089</v>
       </c>
-      <c r="D14" s="4">
-        <v>0.850826</v>
-      </c>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" s="11" t="s">
+      <c r="D14">
+        <v>0.85082599999999997</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>19</v>
       </c>
       <c r="B15">
-        <v>0.754334</v>
+        <v>0.75433399999999995</v>
       </c>
       <c r="C15">
         <v>0.873749</v>
       </c>
       <c r="D15">
-        <v>0.840413</v>
+        <v>0.84041299999999997</v>
       </c>
       <c r="F15">
-        <v>0.758839</v>
+        <v>0.75883900000000004</v>
       </c>
       <c r="G15">
-        <v>0.86963</v>
+        <v>0.86963000000000001</v>
       </c>
       <c r="H15">
-        <v>0.849272</v>
+        <v>0.84927200000000003</v>
       </c>
       <c r="I15">
-        <v>69.85</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
+        <v>69.849999999999994</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>20</v>
       </c>
       <c r="B16">
-        <v>0.752736</v>
+        <v>0.75273599999999996</v>
       </c>
       <c r="C16">
-        <v>0.883474</v>
+        <v>0.88347399999999998</v>
       </c>
       <c r="D16">
-        <v>0.829591</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="12" t="s">
+        <v>0.82959099999999997</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
         <v>21</v>
       </c>
       <c r="B17">
-        <v>0.75113</v>
+        <v>0.75112999999999996</v>
       </c>
       <c r="C17">
-        <v>0.881855</v>
+        <v>0.88185500000000006</v>
       </c>
       <c r="D17">
-        <v>0.828633</v>
+        <v>0.82863299999999995</v>
       </c>
       <c r="F17">
-        <v>0.755163</v>
+        <v>0.75516300000000003</v>
       </c>
       <c r="G17">
-        <v>0.873179</v>
+        <v>0.87317900000000004</v>
       </c>
       <c r="H17">
-        <v>0.840891</v>
+        <v>0.84089100000000006</v>
       </c>
       <c r="I17">
         <v>31.4</v>
       </c>
     </row>
-    <row r="18" spans="1:12">
-      <c r="A18" s="12" t="s">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B18">
-        <v>0.749931</v>
+        <v>0.74993100000000001</v>
       </c>
       <c r="C18">
-        <v>0.889719</v>
+        <v>0.88971900000000004</v>
       </c>
       <c r="D18">
-        <v>0.823178</v>
+        <v>0.82317799999999997</v>
       </c>
       <c r="F18">
-        <v>0.754295</v>
+        <v>0.75429500000000005</v>
       </c>
       <c r="G18">
-        <v>0.867716</v>
+        <v>0.86771600000000004</v>
       </c>
       <c r="H18">
-        <v>0.846821</v>
+        <v>0.84682100000000005</v>
       </c>
       <c r="I18">
         <v>21.2</v>
       </c>
       <c r="J18">
-        <v>0.758375</v>
+        <v>0.75837500000000002</v>
       </c>
       <c r="K18">
-        <v>0.885717</v>
+        <v>0.88571699999999998</v>
       </c>
       <c r="L18">
-        <v>0.836166</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" s="12" t="s">
+        <v>0.83616599999999996</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
         <v>23</v>
       </c>
       <c r="B19">
@@ -1822,129 +1215,129 @@
         <v>0.864012</v>
       </c>
       <c r="D19">
-        <v>0.840153</v>
+        <v>0.84015300000000004</v>
       </c>
       <c r="F19">
-        <v>0.743141</v>
+        <v>0.74314100000000005</v>
       </c>
       <c r="G19">
-        <v>0.870605</v>
+        <v>0.87060499999999996</v>
       </c>
       <c r="H19">
-        <v>0.827508</v>
+        <v>0.82750800000000002</v>
       </c>
       <c r="I19">
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>24</v>
       </c>
       <c r="B20">
-        <v>0.746577</v>
+        <v>0.74657700000000005</v>
       </c>
       <c r="C20">
-        <v>0.866982</v>
+        <v>0.86698200000000003</v>
       </c>
       <c r="D20">
         <v>0.836866</v>
       </c>
     </row>
-    <row r="21" spans="1:12">
-      <c r="A21" s="12" t="s">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
         <v>25</v>
       </c>
       <c r="B21">
-        <v>0.744687</v>
+        <v>0.74468699999999999</v>
       </c>
       <c r="C21">
-        <v>0.880547</v>
+        <v>0.88054699999999997</v>
       </c>
       <c r="D21">
-        <v>0.822196</v>
+        <v>0.82219600000000004</v>
       </c>
       <c r="F21">
-        <v>0.751311</v>
+        <v>0.75131099999999995</v>
       </c>
       <c r="G21">
-        <v>0.882099</v>
+        <v>0.88209899999999997</v>
       </c>
       <c r="H21">
-        <v>0.830119</v>
+        <v>0.83011900000000005</v>
       </c>
       <c r="I21">
         <v>14.5</v>
       </c>
       <c r="J21">
-        <v>0.754584</v>
+        <v>0.75458400000000003</v>
       </c>
       <c r="K21">
-        <v>0.879138</v>
+        <v>0.87913799999999998</v>
       </c>
       <c r="L21">
         <v>0.836511</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
-      <c r="A22" s="12" t="s">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="B22">
-        <v>0.744622</v>
+        <v>0.74462200000000001</v>
       </c>
       <c r="C22">
-        <v>0.870637</v>
+        <v>0.87063699999999999</v>
       </c>
       <c r="D22">
-        <v>0.830575</v>
+        <v>0.83057499999999995</v>
       </c>
       <c r="I22">
         <v>88.3</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
-      <c r="A23" s="8" t="s">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="8">
+      <c r="B23" s="4">
         <v>0.744506</v>
       </c>
-      <c r="C23" s="8">
-        <v>0.860528</v>
-      </c>
-      <c r="D23" s="8">
-        <v>0.839851</v>
-      </c>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8">
-        <v>0.751574</v>
-      </c>
-      <c r="G23" s="8">
-        <v>0.868257</v>
-      </c>
-      <c r="H23" s="8">
-        <v>0.841741</v>
-      </c>
-      <c r="I23" s="8">
+      <c r="C23" s="4">
+        <v>0.86052799999999996</v>
+      </c>
+      <c r="D23" s="4">
+        <v>0.83985100000000001</v>
+      </c>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4">
+        <v>0.75157399999999996</v>
+      </c>
+      <c r="G23" s="4">
+        <v>0.86825699999999995</v>
+      </c>
+      <c r="H23" s="4">
+        <v>0.84174099999999996</v>
+      </c>
+      <c r="I23" s="4">
         <v>57.3</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>28</v>
       </c>
       <c r="B24">
-        <v>0.744324</v>
+        <v>0.74432399999999999</v>
       </c>
       <c r="C24">
-        <v>0.88753</v>
+        <v>0.88753000000000004</v>
       </c>
       <c r="D24">
-        <v>0.817014</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
+        <v>0.81701400000000002</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -1955,60 +1348,60 @@
         <v>0.872448</v>
       </c>
       <c r="D25">
-        <v>0.827411</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12">
-      <c r="A26" s="12" t="s">
+        <v>0.82741100000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
         <v>30</v>
       </c>
       <c r="B26">
-        <v>0.741733</v>
+        <v>0.74173299999999998</v>
       </c>
       <c r="C26">
-        <v>0.864976</v>
+        <v>0.86497599999999997</v>
       </c>
       <c r="D26">
-        <v>0.831163</v>
+        <v>0.83116299999999999</v>
       </c>
       <c r="F26">
         <v>0.745726</v>
       </c>
       <c r="G26">
-        <v>0.859719</v>
+        <v>0.85971900000000001</v>
       </c>
       <c r="H26">
-        <v>0.840692</v>
+        <v>0.84069199999999999</v>
       </c>
       <c r="I26">
         <v>30.7</v>
       </c>
       <c r="J26">
-        <v>0.753258</v>
+        <v>0.75325799999999998</v>
       </c>
       <c r="K26">
         <v>0.86073</v>
       </c>
       <c r="L26">
-        <v>0.850527</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
+        <v>0.85052700000000003</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>31</v>
       </c>
       <c r="B27">
-        <v>0.741629</v>
+        <v>0.74162899999999998</v>
       </c>
       <c r="C27">
-        <v>0.86836</v>
+        <v>0.86836000000000002</v>
       </c>
       <c r="D27">
-        <v>0.827182</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
-      <c r="A28" s="11" t="s">
+        <v>0.82718199999999997</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>32</v>
       </c>
       <c r="B28">
@@ -2018,82 +1411,82 @@
         <v>0.865591</v>
       </c>
       <c r="D28">
-        <v>0.829161</v>
+        <v>0.82916100000000004</v>
       </c>
       <c r="F28">
-        <v>0.751954</v>
+        <v>0.75195400000000001</v>
       </c>
       <c r="G28">
-        <v>0.869312</v>
+        <v>0.86931199999999997</v>
       </c>
       <c r="H28">
-        <v>0.841616</v>
+        <v>0.84161600000000003</v>
       </c>
       <c r="I28">
         <v>50.5</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>33</v>
       </c>
       <c r="B29">
-        <v>0.739805</v>
+        <v>0.73980500000000005</v>
       </c>
       <c r="C29">
-        <v>0.868165</v>
+        <v>0.86816499999999996</v>
       </c>
       <c r="D29">
-        <v>0.82678</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12">
-      <c r="A30" s="12" t="s">
+        <v>0.82677999999999996</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
         <v>34</v>
       </c>
       <c r="B30">
-        <v>0.739755</v>
+        <v>0.73975500000000005</v>
       </c>
       <c r="C30">
-        <v>0.85671</v>
+        <v>0.85670999999999997</v>
       </c>
       <c r="D30">
-        <v>0.83676</v>
+        <v>0.83675999999999995</v>
       </c>
       <c r="I30">
         <v>17.97</v>
       </c>
       <c r="J30">
-        <v>0.749136</v>
+        <v>0.74913600000000002</v>
       </c>
       <c r="K30">
-        <v>0.852683</v>
+        <v>0.85268299999999997</v>
       </c>
       <c r="L30">
-        <v>0.854449</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13">
-      <c r="A31" s="13" t="s">
+        <v>0.85444900000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
         <v>35</v>
       </c>
       <c r="B31">
-        <v>0.738491</v>
+        <v>0.73849100000000001</v>
       </c>
       <c r="C31">
-        <v>0.865018</v>
+        <v>0.86501799999999995</v>
       </c>
       <c r="D31">
         <v>0.827704</v>
       </c>
       <c r="F31">
-        <v>0.74363</v>
+        <v>0.74363000000000001</v>
       </c>
       <c r="G31">
-        <v>0.855144</v>
+        <v>0.85514400000000002</v>
       </c>
       <c r="H31">
-        <v>0.843659</v>
+        <v>0.84365900000000005</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>36</v>
@@ -2102,236 +1495,236 @@
         <v>30.6</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>37</v>
       </c>
       <c r="B32">
-        <v>0.738214</v>
+        <v>0.73821400000000004</v>
       </c>
       <c r="C32">
-        <v>0.86428</v>
+        <v>0.86428000000000005</v>
       </c>
       <c r="D32">
-        <v>0.826714</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9">
+        <v>0.82671399999999995</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>38</v>
       </c>
       <c r="B33">
-        <v>0.735718</v>
+        <v>0.73571799999999998</v>
       </c>
       <c r="C33">
-        <v>0.877324</v>
+        <v>0.87732399999999999</v>
       </c>
       <c r="D33">
-        <v>0.812306</v>
+        <v>0.81230599999999997</v>
       </c>
       <c r="I33">
         <v>16.73</v>
       </c>
     </row>
-    <row r="34" spans="1:12">
-      <c r="A34" s="12" t="s">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" s="6" t="s">
         <v>39</v>
       </c>
       <c r="B34">
-        <v>0.734301</v>
+        <v>0.73430099999999998</v>
       </c>
       <c r="C34">
-        <v>0.871991</v>
+        <v>0.87199099999999996</v>
       </c>
       <c r="D34">
-        <v>0.816322</v>
+        <v>0.81632199999999999</v>
       </c>
       <c r="I34">
         <v>31</v>
       </c>
       <c r="J34">
-        <v>0.750739</v>
+        <v>0.75073900000000005</v>
       </c>
       <c r="K34">
-        <v>0.873047</v>
+        <v>0.87304700000000002</v>
       </c>
       <c r="L34">
-        <v>0.836097</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
+        <v>0.83609699999999998</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>40</v>
       </c>
       <c r="B35">
-        <v>0.732523</v>
+        <v>0.73252300000000004</v>
       </c>
       <c r="C35">
-        <v>0.867589</v>
+        <v>0.86758900000000005</v>
       </c>
       <c r="D35">
-        <v>0.818167</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
+        <v>0.81816699999999998</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>41</v>
       </c>
       <c r="B36">
-        <v>0.732164</v>
+        <v>0.73216400000000004</v>
       </c>
       <c r="C36">
-        <v>0.860681</v>
+        <v>0.86068100000000003</v>
       </c>
       <c r="D36">
-        <v>0.823889</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
+        <v>0.82388899999999998</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>42</v>
       </c>
       <c r="B37">
-        <v>0.730829</v>
+        <v>0.73082899999999995</v>
       </c>
       <c r="C37">
-        <v>0.869431</v>
+        <v>0.86943099999999995</v>
       </c>
       <c r="D37">
-        <v>0.814548</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9">
+        <v>0.81454800000000005</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>43</v>
       </c>
       <c r="B38">
-        <v>0.726804</v>
+        <v>0.72680400000000001</v>
       </c>
       <c r="C38">
         <v>0.857101</v>
       </c>
       <c r="D38">
-        <v>0.819385</v>
+        <v>0.81938500000000003</v>
       </c>
       <c r="I38">
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>44</v>
       </c>
       <c r="B39">
-        <v>0.723994</v>
+        <v>0.72399400000000003</v>
       </c>
       <c r="C39">
-        <v>0.857618</v>
+        <v>0.85761799999999999</v>
       </c>
       <c r="D39">
-        <v>0.81522</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
+        <v>0.81521999999999994</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>45</v>
       </c>
       <c r="B40">
-        <v>0.719465</v>
+        <v>0.71946500000000002</v>
       </c>
       <c r="C40">
-        <v>0.86807</v>
+        <v>0.86807000000000001</v>
       </c>
       <c r="D40">
-        <v>0.800449</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9">
+        <v>0.80044899999999997</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>46</v>
       </c>
       <c r="B41">
-        <v>0.716961</v>
+        <v>0.71696099999999996</v>
       </c>
       <c r="C41">
         <v>0.870251</v>
       </c>
       <c r="D41">
-        <v>0.794472</v>
+        <v>0.79447199999999996</v>
       </c>
       <c r="I41">
         <v>34</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>47</v>
       </c>
       <c r="B42">
-        <v>0.71694</v>
+        <v>0.71694000000000002</v>
       </c>
       <c r="C42">
-        <v>0.861888</v>
+        <v>0.86188799999999999</v>
       </c>
       <c r="D42">
-        <v>0.80138</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12">
-      <c r="A43" s="12" t="s">
+        <v>0.80137999999999998</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A43" s="6" t="s">
         <v>48</v>
       </c>
       <c r="B43">
-        <v>0.716365</v>
+        <v>0.71636500000000003</v>
       </c>
       <c r="C43">
-        <v>0.85087</v>
+        <v>0.85087000000000002</v>
       </c>
       <c r="D43">
-        <v>0.81112</v>
+        <v>0.81111999999999995</v>
       </c>
       <c r="I43">
         <v>7.71</v>
       </c>
       <c r="J43">
-        <v>0.736053</v>
+        <v>0.73605299999999996</v>
       </c>
       <c r="K43">
-        <v>0.857934</v>
+        <v>0.85793399999999997</v>
       </c>
       <c r="L43">
-        <v>0.831937</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
+        <v>0.83193700000000004</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>49</v>
       </c>
       <c r="B44">
-        <v>0.713546</v>
+        <v>0.71354600000000001</v>
       </c>
       <c r="C44">
         <v>0.869784</v>
       </c>
       <c r="D44">
-        <v>0.791984</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
+        <v>0.79198400000000002</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>50</v>
       </c>
       <c r="B45">
-        <v>0.711791</v>
+        <v>0.71179099999999995</v>
       </c>
       <c r="C45">
-        <v>0.866464</v>
+        <v>0.86646400000000001</v>
       </c>
       <c r="D45">
-        <v>0.791122</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
+        <v>0.79112199999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>51</v>
       </c>
@@ -2339,82 +1732,82 @@
         <v>0.711113</v>
       </c>
       <c r="C46">
-        <v>0.846254</v>
+        <v>0.84625399999999995</v>
       </c>
       <c r="D46">
         <v>0.806975</v>
       </c>
     </row>
-    <row r="47" spans="1:12">
-      <c r="A47" s="12" t="s">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A47" s="6" t="s">
         <v>52</v>
       </c>
       <c r="B47">
-        <v>0.710599</v>
+        <v>0.71059899999999998</v>
       </c>
       <c r="C47">
-        <v>0.868084</v>
+        <v>0.86808399999999997</v>
       </c>
       <c r="D47">
-        <v>0.789526</v>
+        <v>0.78952599999999995</v>
       </c>
       <c r="I47">
         <v>25</v>
       </c>
       <c r="J47">
-        <v>0.716838</v>
+        <v>0.71683799999999998</v>
       </c>
       <c r="K47">
         <v>0.848993</v>
       </c>
       <c r="L47">
-        <v>0.813434</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12">
-      <c r="A48" s="12" t="s">
+        <v>0.81343399999999999</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A48" s="6" t="s">
         <v>53</v>
       </c>
       <c r="B48">
-        <v>0.699765</v>
+        <v>0.69976499999999997</v>
       </c>
       <c r="C48">
-        <v>0.849119</v>
+        <v>0.84911899999999996</v>
       </c>
       <c r="D48">
         <v>0.788358</v>
       </c>
       <c r="F48">
-        <v>0.698915</v>
+        <v>0.69891499999999995</v>
       </c>
       <c r="G48">
         <v>0.847132</v>
       </c>
       <c r="H48">
-        <v>0.788943</v>
+        <v>0.78894299999999995</v>
       </c>
       <c r="I48">
         <v>9.74</v>
       </c>
       <c r="J48">
-        <v>0.713066</v>
+        <v>0.71306599999999998</v>
       </c>
       <c r="K48">
         <v>0.852715</v>
       </c>
       <c r="L48">
-        <v>0.805148</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12">
-      <c r="A49" s="12" t="s">
+        <v>0.80514799999999997</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A49" s="6" t="s">
         <v>54</v>
       </c>
       <c r="B49">
-        <v>0.699049</v>
+        <v>0.69904900000000003</v>
       </c>
       <c r="C49">
-        <v>0.859332</v>
+        <v>0.85933199999999998</v>
       </c>
       <c r="D49">
         <v>0.781447</v>
@@ -2423,30 +1816,30 @@
         <v>12.94</v>
       </c>
       <c r="J49">
-        <v>0.691986</v>
+        <v>0.69198599999999999</v>
       </c>
       <c r="K49">
-        <v>0.839438</v>
+        <v>0.83943800000000002</v>
       </c>
       <c r="L49">
-        <v>0.788699</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8">
+        <v>0.78869900000000004</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>55</v>
       </c>
       <c r="B50">
-        <v>0.694979</v>
+        <v>0.69497900000000001</v>
       </c>
       <c r="C50">
-        <v>0.865616</v>
+        <v>0.86561600000000005</v>
       </c>
       <c r="D50">
-        <v>0.771683</v>
+        <v>0.77168300000000001</v>
       </c>
       <c r="F50">
-        <v>0.697399</v>
+        <v>0.69739899999999999</v>
       </c>
       <c r="G50">
         <v>0.868533</v>
@@ -2455,87 +1848,109 @@
         <v>0.771671</v>
       </c>
     </row>
-    <row r="51" spans="1:12">
-      <c r="A51" s="12" t="s">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A51" s="6" t="s">
         <v>56</v>
       </c>
       <c r="B51">
-        <v>0.734976</v>
+        <v>0.73497599999999996</v>
       </c>
       <c r="C51">
-        <v>0.863216</v>
+        <v>0.86321599999999998</v>
       </c>
       <c r="D51">
-        <v>0.824038</v>
+        <v>0.82403800000000005</v>
       </c>
       <c r="I51">
         <v>22.9</v>
       </c>
       <c r="J51">
-        <v>0.745505</v>
+        <v>0.74550499999999997</v>
       </c>
       <c r="K51">
-        <v>0.860679</v>
+        <v>0.86067899999999997</v>
       </c>
       <c r="L51">
-        <v>0.84022</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12">
-      <c r="A52" s="12" t="s">
+        <v>0.84021999999999997</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A52" s="6" t="s">
         <v>57</v>
       </c>
       <c r="B52">
-        <v>0.721233</v>
+        <v>0.72123300000000001</v>
       </c>
       <c r="C52">
-        <v>0.857926</v>
+        <v>0.85792599999999997</v>
       </c>
       <c r="D52">
-        <v>0.810198</v>
+        <v>0.81019799999999997</v>
       </c>
       <c r="I52">
         <v>11.42</v>
       </c>
       <c r="J52">
-        <v>0.734794</v>
+        <v>0.73479399999999995</v>
       </c>
       <c r="K52">
-        <v>0.857295</v>
+        <v>0.85729500000000003</v>
       </c>
       <c r="L52">
-        <v>0.830844</v>
+        <v>0.83084400000000003</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="B53">
+        <v>0.74578599999999995</v>
+      </c>
+      <c r="C53">
+        <v>0.87922</v>
+      </c>
+      <c r="D53">
+        <v>0.82449899999999998</v>
+      </c>
+      <c r="J53">
+        <v>0.74951400000000001</v>
+      </c>
+      <c r="K53">
+        <v>0.88462300000000005</v>
+      </c>
+      <c r="L53">
+        <v>0.82542499999999996</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A1:L50">
-    <sortCondition ref="B1:B50" descending="1"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:L50">
+    <sortCondition descending="1" ref="B1:B50"/>
   </sortState>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J37"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39.7777777777778" customWidth="1"/>
-    <col min="2" max="2" width="12.3333333333333" customWidth="1"/>
-    <col min="3" max="3" width="13.8888888888889" customWidth="1"/>
-    <col min="4" max="4" width="13.1111111111111" customWidth="1"/>
-    <col min="5" max="5" width="16.7777777777778" customWidth="1"/>
-    <col min="6" max="6" width="15.7777777777778" customWidth="1"/>
-    <col min="7" max="7" width="16.2222222222222" customWidth="1"/>
-    <col min="8" max="8" width="25.8888888888889" customWidth="1"/>
-    <col min="10" max="10" width="15.6666666666667" customWidth="1"/>
-    <col min="11" max="11" width="16.4444444444444" customWidth="1"/>
+    <col min="1" max="1" width="39.77734375" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" customWidth="1"/>
+    <col min="3" max="3" width="13.88671875" customWidth="1"/>
+    <col min="4" max="4" width="13.109375" customWidth="1"/>
+    <col min="5" max="5" width="16.77734375" customWidth="1"/>
+    <col min="6" max="6" width="15.77734375" customWidth="1"/>
+    <col min="7" max="7" width="16.21875" customWidth="1"/>
+    <col min="8" max="8" width="25.88671875" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" customWidth="1"/>
+    <col min="11" max="11" width="16.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -2560,12 +1975,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>61</v>
       </c>
       <c r="B2">
-        <v>0.7731</v>
+        <v>0.77310000000000001</v>
       </c>
       <c r="F2">
         <v>3.31</v>
@@ -2574,14 +1989,14 @@
         <v>1.28</v>
       </c>
       <c r="I2">
-        <v>0.7533</v>
+        <v>0.75329999999999997</v>
       </c>
       <c r="J2">
-        <v>0.8711</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="6" t="s">
+        <v>0.87109999999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>62</v>
       </c>
       <c r="B3">
@@ -2594,12 +2009,12 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="5" t="s">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>63</v>
       </c>
       <c r="B4">
-        <v>0.7558</v>
+        <v>0.75580000000000003</v>
       </c>
       <c r="E4">
         <v>30.2</v>
@@ -2611,39 +2026,39 @@
         <v>3.74</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="7" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="4">
         <v>0.744506</v>
       </c>
-      <c r="C5" s="8">
-        <v>0.860528</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.839851</v>
-      </c>
-      <c r="E5" s="8">
+      <c r="C5" s="4">
+        <v>0.86052799999999996</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.83985100000000001</v>
+      </c>
+      <c r="E5" s="4">
         <v>57.3</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="4">
         <v>7.56</v>
       </c>
-      <c r="G5" s="8">
-        <v>4.11</v>
-      </c>
-      <c r="H5" s="8"/>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="6" t="s">
+      <c r="G5" s="4">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="H5" s="4"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>64</v>
       </c>
       <c r="B6">
-        <v>0.7432</v>
+        <v>0.74319999999999997</v>
       </c>
       <c r="E6">
-        <v>17.9</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="F6">
         <v>3.41</v>
@@ -2652,26 +2067,26 @@
         <v>2.91</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>65</v>
       </c>
       <c r="B7">
-        <v>0.7426</v>
+        <v>0.74260000000000004</v>
       </c>
       <c r="F7">
-        <v>2.01</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="G7">
         <v>1.21</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>66</v>
       </c>
       <c r="B8">
-        <v>0.742</v>
+        <v>0.74199999999999999</v>
       </c>
       <c r="F8">
         <v>1.5</v>
@@ -2680,15 +2095,15 @@
         <v>0.88</v>
       </c>
       <c r="J8">
-        <v>0.8415</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="6" t="s">
+        <v>0.84150000000000003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>67</v>
       </c>
       <c r="B9">
-        <v>0.7406</v>
+        <v>0.74060000000000004</v>
       </c>
       <c r="E9">
         <v>12.8</v>
@@ -2703,8 +2118,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="6" t="s">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>69</v>
       </c>
       <c r="B10">
@@ -2720,18 +2135,16 @@
         <v>1</v>
       </c>
       <c r="J10">
-        <v>0.8666</v>
-      </c>
-    </row>
-    <row r="11" s="4" customFormat="1" spans="1:9">
-      <c r="A11" s="6" t="s">
+        <v>0.86660000000000004</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>70</v>
       </c>
       <c r="B11">
-        <v>0.7358</v>
-      </c>
-      <c r="C11"/>
-      <c r="D11"/>
+        <v>0.73580000000000001</v>
+      </c>
       <c r="E11">
         <v>56.1</v>
       </c>
@@ -2741,15 +2154,13 @@
       <c r="G11">
         <v>4.08</v>
       </c>
-      <c r="H11"/>
-      <c r="I11"/>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="5" t="s">
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>71</v>
       </c>
       <c r="B12">
-        <v>0.7308</v>
+        <v>0.73080000000000001</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -2758,15 +2169,15 @@
         <v>1.5</v>
       </c>
       <c r="G12">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>72</v>
       </c>
       <c r="B13">
-        <v>0.7294</v>
+        <v>0.72940000000000005</v>
       </c>
       <c r="F13">
         <v>1.72</v>
@@ -2775,39 +2186,35 @@
         <v>1.22</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="6" t="s">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>73</v>
       </c>
-      <c r="B14" s="4">
-        <v>0.7271</v>
-      </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4">
+      <c r="B14">
+        <v>0.72709999999999997</v>
+      </c>
+      <c r="E14">
         <v>8.9</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14">
         <v>1.81</v>
       </c>
-      <c r="G14" s="4">
+      <c r="G14">
         <v>1</v>
       </c>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="5" t="s">
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>74</v>
       </c>
       <c r="B15">
-        <v>0.726864</v>
+        <v>0.72686399999999995</v>
       </c>
       <c r="C15">
-        <v>0.851062</v>
+        <v>0.85106199999999999</v>
       </c>
       <c r="D15">
-        <v>0.824586</v>
+        <v>0.82458600000000004</v>
       </c>
       <c r="E15">
         <v>45</v>
@@ -2819,36 +2226,36 @@
         <v>3.76</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="9" t="s">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B16" s="10">
-        <v>0.722361</v>
-      </c>
-      <c r="C16" s="10">
-        <v>0.867663</v>
-      </c>
-      <c r="D16" s="10">
-        <v>0.803904</v>
-      </c>
-      <c r="E16" s="10">
-        <v>17.4</v>
-      </c>
-      <c r="F16" s="10">
+      <c r="B16" s="5">
+        <v>0.72236100000000003</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0.86766299999999996</v>
+      </c>
+      <c r="D16" s="5">
+        <v>0.80390399999999995</v>
+      </c>
+      <c r="E16" s="5">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="F16" s="5">
         <v>2.29</v>
       </c>
-      <c r="G16" s="10">
+      <c r="G16" s="5">
         <v>1.41</v>
       </c>
-      <c r="H16" s="10"/>
-    </row>
-    <row r="17" spans="1:7">
+      <c r="H16" s="5"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>76</v>
       </c>
       <c r="B17">
-        <v>0.7215</v>
+        <v>0.72150000000000003</v>
       </c>
       <c r="F17">
         <v>2.35</v>
@@ -2857,15 +2264,13 @@
         <v>2.09</v>
       </c>
     </row>
-    <row r="18" s="4" customFormat="1" ht="12" customHeight="1" spans="1:9">
-      <c r="A18" s="6" t="s">
+    <row r="18" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>77</v>
       </c>
       <c r="B18">
-        <v>0.7161</v>
-      </c>
-      <c r="C18"/>
-      <c r="D18"/>
+        <v>0.71609999999999996</v>
+      </c>
       <c r="E18">
         <v>6.9</v>
       </c>
@@ -2875,15 +2280,13 @@
       <c r="G18">
         <v>1.43</v>
       </c>
-      <c r="H18"/>
-      <c r="I18"/>
-    </row>
-    <row r="19" spans="1:7">
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>78</v>
       </c>
       <c r="B19">
-        <v>0.7138</v>
+        <v>0.71379999999999999</v>
       </c>
       <c r="F19">
         <v>1.75</v>
@@ -2892,18 +2295,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="5" t="s">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>79</v>
       </c>
       <c r="B20">
-        <v>0.710494</v>
+        <v>0.71049399999999996</v>
       </c>
       <c r="C20">
-        <v>0.863519</v>
+        <v>0.86351900000000004</v>
       </c>
       <c r="D20">
-        <v>0.792156</v>
+        <v>0.79215599999999997</v>
       </c>
       <c r="E20">
         <v>14</v>
@@ -2915,12 +2318,12 @@
         <v>1.88</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>80</v>
       </c>
       <c r="B21">
-        <v>0.7101</v>
+        <v>0.71009999999999995</v>
       </c>
       <c r="F21">
         <v>5.18</v>
@@ -2929,8 +2332,8 @@
         <v>2.76</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="6" t="s">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>81</v>
       </c>
       <c r="B22">
@@ -2946,12 +2349,12 @@
         <v>2.06</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
-      <c r="A23" s="6" t="s">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>82</v>
       </c>
       <c r="B23">
-        <v>0.7089</v>
+        <v>0.70889999999999997</v>
       </c>
       <c r="E23">
         <v>7.2</v>
@@ -2962,40 +2365,33 @@
       <c r="G23">
         <v>0.94</v>
       </c>
-      <c r="I23" s="4"/>
-    </row>
-    <row r="24" s="4" customFormat="1" spans="1:10">
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>83</v>
       </c>
       <c r="B24">
-        <v>0.707672</v>
+        <v>0.70767199999999997</v>
       </c>
       <c r="C24">
-        <v>0.856807</v>
+        <v>0.85680699999999999</v>
       </c>
       <c r="D24">
-        <v>0.794199</v>
-      </c>
-      <c r="E24"/>
-      <c r="F24"/>
-      <c r="G24"/>
-      <c r="H24"/>
-      <c r="I24"/>
-      <c r="J24"/>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="5" t="s">
+        <v>0.79419899999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>84</v>
       </c>
       <c r="B25">
-        <v>0.707574</v>
+        <v>0.70757400000000004</v>
       </c>
       <c r="C25">
-        <v>0.865108</v>
+        <v>0.86510799999999999</v>
       </c>
       <c r="D25">
-        <v>0.787678</v>
+        <v>0.78767799999999999</v>
       </c>
       <c r="E25">
         <v>16</v>
@@ -3007,12 +2403,12 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>85</v>
       </c>
       <c r="B26">
-        <v>0.7066</v>
+        <v>0.70660000000000001</v>
       </c>
       <c r="F26">
         <v>1.41</v>
@@ -3021,18 +2417,18 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="5" t="s">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>86</v>
       </c>
       <c r="B27">
-        <v>0.698648</v>
+        <v>0.69864800000000005</v>
       </c>
       <c r="C27">
-        <v>0.862994</v>
+        <v>0.86299400000000004</v>
       </c>
       <c r="D27">
-        <v>0.776894</v>
+        <v>0.77689399999999997</v>
       </c>
       <c r="E27">
         <v>12.7</v>
@@ -3043,34 +2439,30 @@
       <c r="G27">
         <v>1.64</v>
       </c>
-      <c r="J27" s="4"/>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="6" t="s">
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="4">
-        <v>0.683513</v>
-      </c>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4">
+      <c r="B28">
+        <v>0.68351300000000004</v>
+      </c>
+      <c r="E28">
         <v>10.4</v>
       </c>
-      <c r="F28" s="4">
+      <c r="F28">
         <v>1.72</v>
       </c>
-      <c r="G28" s="4">
+      <c r="G28">
         <v>1.33</v>
       </c>
-      <c r="H28" s="4"/>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="5" t="s">
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>88</v>
       </c>
       <c r="B29">
-        <v>0.683125</v>
+        <v>0.68312499999999998</v>
       </c>
       <c r="C29">
         <v>0.869475</v>
@@ -3088,12 +2480,12 @@
         <v>1.84</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>89</v>
       </c>
       <c r="B30">
-        <v>0.6737</v>
+        <v>0.67369999999999997</v>
       </c>
       <c r="F30">
         <v>0.98</v>
@@ -3102,18 +2494,18 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="5" t="s">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>90</v>
       </c>
       <c r="B31">
-        <v>0.673307</v>
+        <v>0.67330699999999999</v>
       </c>
       <c r="C31">
-        <v>0.844487</v>
+        <v>0.84448699999999999</v>
       </c>
       <c r="D31">
-        <v>0.758419</v>
+        <v>0.75841899999999995</v>
       </c>
       <c r="E31">
         <v>6.3</v>
@@ -3125,39 +2517,35 @@
         <v>0.93</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
-      <c r="A32" s="6" t="s">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>91</v>
       </c>
-      <c r="B32" s="4">
-        <v>0.667316</v>
-      </c>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4">
-        <v>4.9</v>
-      </c>
-      <c r="F32" s="4">
+      <c r="B32">
+        <v>0.66731600000000002</v>
+      </c>
+      <c r="E32">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="F32">
         <v>0.8</v>
       </c>
-      <c r="G32" s="4">
+      <c r="G32">
         <v>0.67</v>
       </c>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33" s="5" t="s">
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>92</v>
       </c>
       <c r="B33">
-        <v>0.660027</v>
+        <v>0.66002700000000003</v>
       </c>
       <c r="C33">
-        <v>0.838495</v>
+        <v>0.83849499999999999</v>
       </c>
       <c r="D33">
-        <v>0.744536</v>
+        <v>0.74453599999999998</v>
       </c>
       <c r="E33">
         <v>11</v>
@@ -3169,18 +2557,18 @@
         <v>1.22</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
-      <c r="A34" s="5" t="s">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>93</v>
       </c>
       <c r="B34">
         <v>0.65747</v>
       </c>
       <c r="C34">
-        <v>0.830172</v>
+        <v>0.83017200000000002</v>
       </c>
       <c r="D34">
-        <v>0.745829</v>
+        <v>0.74582899999999996</v>
       </c>
       <c r="E34">
         <v>8</v>
@@ -3192,81 +2580,78 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="9" t="s">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="B35" s="10">
+      <c r="B35" s="5">
         <v>0</v>
       </c>
-      <c r="C35" s="10"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10">
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5">
         <v>4.3</v>
       </c>
-      <c r="F35" s="10">
+      <c r="F35" s="5">
         <v>0.78</v>
       </c>
-      <c r="G35" s="10">
+      <c r="G35" s="5">
         <v>0.65</v>
       </c>
-      <c r="H35" s="10"/>
-    </row>
-    <row r="36" spans="1:5">
+      <c r="H35" s="5"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>95</v>
       </c>
       <c r="B36">
-        <v>0.712137</v>
+        <v>0.71213700000000002</v>
       </c>
       <c r="C36">
-        <v>0.86402</v>
+        <v>0.86402000000000001</v>
       </c>
       <c r="D36">
-        <v>0.794336</v>
+        <v>0.79433600000000004</v>
       </c>
       <c r="E36">
         <v>30</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>96</v>
       </c>
       <c r="B37">
-        <v>0.715039</v>
+        <v>0.71503899999999998</v>
       </c>
       <c r="C37">
-        <v>0.870833</v>
+        <v>0.87083299999999997</v>
       </c>
       <c r="D37">
-        <v>0.791829</v>
+        <v>0.79182900000000001</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G37">
-    <extLst/>
-  </autoFilter>
-  <sortState ref="A1:J35">
-    <sortCondition ref="B1:B35" descending="1"/>
+  <autoFilter ref="A1:G37" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:J35">
+    <sortCondition descending="1" ref="B1:B35"/>
   </sortState>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C34"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="13.8" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="38.2222222222222" customWidth="1"/>
-    <col min="2" max="2" width="32.6666666666667" customWidth="1"/>
-    <col min="3" max="3" width="20.8888888888889" customWidth="1"/>
+    <col min="1" max="1" width="38.21875" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" customWidth="1"/>
+    <col min="3" max="3" width="20.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>97</v>
       </c>
@@ -3277,7 +2662,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>35</v>
       </c>
@@ -3285,7 +2670,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -3293,7 +2678,7 @@
         <v>5.24</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>26</v>
       </c>
@@ -3301,7 +2686,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>101</v>
       </c>
@@ -3309,7 +2694,7 @@
         <v>4.53</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>56</v>
       </c>
@@ -3317,7 +2702,7 @@
         <v>4.42</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
@@ -3325,7 +2710,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>102</v>
       </c>
@@ -3333,7 +2718,7 @@
         <v>2.92</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>95</v>
       </c>
@@ -3341,7 +2726,7 @@
         <v>2.52</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>39</v>
       </c>
@@ -3349,15 +2734,15 @@
         <v>2.35</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B11" s="1">
-        <v>2.22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
+        <v>2.2200000000000002</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>52</v>
       </c>
@@ -3365,7 +2750,7 @@
         <v>2.02</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>103</v>
       </c>
@@ -3373,7 +2758,7 @@
         <v>1.81</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>75</v>
       </c>
@@ -3381,7 +2766,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>104</v>
       </c>
@@ -3389,7 +2774,7 @@
         <v>1.58</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>105</v>
       </c>
@@ -3397,7 +2782,7 @@
         <v>1.54</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>83</v>
       </c>
@@ -3405,7 +2790,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>106</v>
       </c>
@@ -3413,7 +2798,7 @@
         <v>1.41</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>54</v>
       </c>
@@ -3421,7 +2806,7 @@
         <v>1.37</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>57</v>
       </c>
@@ -3429,7 +2814,7 @@
         <v>1.37</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>107</v>
       </c>
@@ -3437,7 +2822,7 @@
         <v>1.37</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>22</v>
       </c>
@@ -3445,7 +2830,7 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>108</v>
       </c>
@@ -3453,7 +2838,7 @@
         <v>1.22</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>25</v>
       </c>
@@ -3461,15 +2846,15 @@
         <v>1.19</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>109</v>
       </c>
       <c r="B25" s="1">
-        <v>1.14</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
+        <v>1.1399999999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>110</v>
       </c>
@@ -3477,15 +2862,15 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>111</v>
       </c>
       <c r="B27" s="1">
-        <v>0.989</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
+        <v>0.98899999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>48</v>
       </c>
@@ -3493,7 +2878,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>53</v>
       </c>
@@ -3501,50 +2886,49 @@
         <v>0.89</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>112</v>
       </c>
       <c r="B30" s="1">
-        <v>0.799</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
+        <v>0.79900000000000004</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
     </row>
   </sheetData>
-  <sortState ref="A2:B30">
-    <sortCondition ref="B2:B30" descending="1"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B30">
+    <sortCondition descending="1" ref="B2:B30"/>
   </sortState>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="13.8" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="51.6666666666667" customWidth="1"/>
-    <col min="2" max="2" width="27.6666666666667" customWidth="1"/>
+    <col min="1" max="1" width="51.6640625" customWidth="1"/>
+    <col min="2" max="2" width="27.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>97</v>
       </c>
@@ -3552,23 +2936,23 @@
         <v>113</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B2">
-        <v>1.12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>116</v>
       </c>
@@ -3576,72 +2960,74 @@
         <v>3.26</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B5">
-        <v>4.6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>3.26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B6">
-        <v>3.26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B7">
+        <v>1.74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>122</v>
+      </c>
+      <c r="B8">
+        <v>1.1399999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>114</v>
+      </c>
+      <c r="B9">
+        <v>1.1200000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>119</v>
       </c>
-      <c r="B7">
+      <c r="B10">
         <v>0.49</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>120</v>
-      </c>
-      <c r="B8">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>121</v>
-      </c>
-      <c r="B9">
-        <v>1.74</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
-        <v>122</v>
-      </c>
-      <c r="B10">
-        <v>1.14</v>
-      </c>
-    </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B10">
+    <sortCondition descending="1" ref="B2:B10"/>
+  </sortState>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="13.8" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.1111111111111" customWidth="1"/>
-    <col min="2" max="2" width="19.1111111111111" customWidth="1"/>
-    <col min="3" max="3" width="25.1111111111111" customWidth="1"/>
+    <col min="1" max="1" width="32.109375" customWidth="1"/>
+    <col min="2" max="2" width="19.109375" customWidth="1"/>
+    <col min="3" max="3" width="25.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>97</v>
       </c>
@@ -3652,7 +3038,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>125</v>
       </c>
@@ -3663,15 +3049,15 @@
         <v>1.28</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>126</v>
       </c>
       <c r="B3" s="1">
-        <v>2.47</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>2.4700000000000002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>127</v>
       </c>
@@ -3679,7 +3065,7 @@
         <v>2.12</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>128</v>
       </c>
@@ -3687,7 +3073,7 @@
         <v>2.06</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>129</v>
       </c>
@@ -3695,7 +3081,7 @@
         <v>1.37</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>130</v>
       </c>
@@ -3703,7 +3089,7 @@
         <v>1.26</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>131</v>
       </c>
@@ -3711,7 +3097,7 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>132</v>
       </c>
@@ -3719,15 +3105,15 @@
         <v>0.69</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>133</v>
       </c>
       <c r="B10" s="1">
-        <v>0.58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+        <v>0.57999999999999996</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>134</v>
       </c>
@@ -3735,32 +3121,32 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="12" spans="2:2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B12" s="1"/>
     </row>
-    <row r="13" spans="2:2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B13" s="1"/>
     </row>
-    <row r="14" spans="2:2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B14" s="1"/>
     </row>
-    <row r="15" spans="2:2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B15" s="1"/>
     </row>
-    <row r="16" spans="2:2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B16" s="1"/>
     </row>
-    <row r="17" spans="2:2">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" s="1"/>
     </row>
-    <row r="18" spans="2:2">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" s="1"/>
     </row>
   </sheetData>
-  <sortState ref="A2:B11">
-    <sortCondition ref="B2:B11" descending="1"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B11">
+    <sortCondition descending="1" ref="B2:B11"/>
   </sortState>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/测试数据.xlsx
+++ b/测试数据.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\F\ABlueFaceProj\20240618\Seg\Beta_BiSeNet-master_Slim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{781BEED3-F9DC-4C40-8566-B0B5A9AD232D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D7B6AFE-E16F-42D2-89A6-0BE89C5E06D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="大模型" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="137">
   <si>
     <t>x2</t>
   </si>
@@ -435,6 +435,10 @@
   </si>
   <si>
     <t>fastefficientbisenet_inceptionnext_atto_v2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fastefficientbisenet_vit_s_dinov3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -806,7 +810,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="59.109375" customWidth="1"/>
@@ -1921,6 +1925,20 @@
       </c>
       <c r="L53">
         <v>0.82542499999999996</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A54" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="B54">
+        <v>0.74725900000000001</v>
+      </c>
+      <c r="C54">
+        <v>0.86913899999999999</v>
+      </c>
+      <c r="D54">
+        <v>0.835422</v>
       </c>
     </row>
   </sheetData>

--- a/测试数据.xlsx
+++ b/测试数据.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\F\ABlueFaceProj\20240618\Seg\Beta_BiSeNet-master_Slim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D7B6AFE-E16F-42D2-89A6-0BE89C5E06D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3C52647-B5AA-4931-8567-B658C8379129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="大模型" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="140">
   <si>
     <t>x2</t>
   </si>
@@ -439,6 +439,18 @@
   </si>
   <si>
     <t>fastefficientbisenet_vit_s_dinov3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5070/515x512,fp32</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fp16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dinov3segnet_vit_b</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -519,7 +531,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -535,6 +547,8 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -810,11 +824,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:O55"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="59.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.88671875" customWidth="1"/>
+    <col min="2" max="2" width="15.109375" customWidth="1"/>
     <col min="3" max="3" width="10.88671875" customWidth="1"/>
     <col min="4" max="4" width="10.44140625" customWidth="1"/>
     <col min="6" max="8" width="9.6640625"/>
@@ -822,9 +836,10 @@
     <col min="10" max="11" width="9.6640625"/>
     <col min="12" max="12" width="15.21875" customWidth="1"/>
     <col min="13" max="13" width="13.44140625" customWidth="1"/>
+    <col min="14" max="14" width="22.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -840,8 +855,14 @@
       <c r="I1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N1" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="O1" s="9" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -867,7 +888,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -890,7 +911,7 @@
         <v>0.86963800000000002</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -907,7 +928,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
@@ -941,8 +962,11 @@
       <c r="L5">
         <v>0.85651299999999997</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N5">
+        <v>1.4411799999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -965,7 +989,7 @@
         <v>0.86818799999999996</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -991,7 +1015,7 @@
         <v>85.6</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -1008,7 +1032,7 @@
         <v>58.84</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -1025,7 +1049,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -1042,7 +1066,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -1056,7 +1080,7 @@
         <v>0.84851699999999997</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -1079,7 +1103,7 @@
         <v>0.83723499999999995</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -1093,7 +1117,7 @@
         <v>0.83460699999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -1107,7 +1131,7 @@
         <v>0.85082599999999997</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -1133,7 +1157,7 @@
         <v>69.849999999999994</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -1147,7 +1171,7 @@
         <v>0.82959099999999997</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>21</v>
       </c>
@@ -1173,7 +1197,7 @@
         <v>31.4</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>22</v>
       </c>
@@ -1208,7 +1232,7 @@
         <v>0.83616599999999996</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>23</v>
       </c>
@@ -1234,7 +1258,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -1248,7 +1272,7 @@
         <v>0.836866</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>25</v>
       </c>
@@ -1282,8 +1306,14 @@
       <c r="L21">
         <v>0.836511</v>
       </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N21">
+        <v>0.75868000000000002</v>
+      </c>
+      <c r="O21">
+        <v>0.35229700000000003</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>26</v>
       </c>
@@ -1300,7 +1330,7 @@
         <v>88.3</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>27</v>
       </c>
@@ -1327,7 +1357,7 @@
         <v>57.3</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>28</v>
       </c>
@@ -1341,7 +1371,7 @@
         <v>0.81701400000000002</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -1355,7 +1385,7 @@
         <v>0.82741100000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>30</v>
       </c>
@@ -1390,7 +1420,7 @@
         <v>0.85052700000000003</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>31</v>
       </c>
@@ -1404,7 +1434,7 @@
         <v>0.82718199999999997</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -1430,7 +1460,7 @@
         <v>50.5</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>33</v>
       </c>
@@ -1444,7 +1474,7 @@
         <v>0.82677999999999996</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
         <v>34</v>
       </c>
@@ -1470,7 +1500,7 @@
         <v>0.85444900000000001</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
         <v>35</v>
       </c>
@@ -1499,7 +1529,7 @@
         <v>30.6</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>37</v>
       </c>
@@ -1803,7 +1833,7 @@
         <v>0.80514799999999997</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
         <v>54</v>
       </c>
@@ -1829,7 +1859,7 @@
         <v>0.78869900000000004</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>55</v>
       </c>
@@ -1852,7 +1882,7 @@
         <v>0.771671</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
         <v>56</v>
       </c>
@@ -1878,7 +1908,7 @@
         <v>0.84021999999999997</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>57</v>
       </c>
@@ -1904,7 +1934,7 @@
         <v>0.83084400000000003</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
         <v>135</v>
       </c>
@@ -1927,7 +1957,7 @@
         <v>0.82542499999999996</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="8" t="s">
         <v>136</v>
       </c>
@@ -1939,6 +1969,23 @@
       </c>
       <c r="D54">
         <v>0.835422</v>
+      </c>
+      <c r="N54">
+        <v>3.6217100000000002</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A55" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="B55">
+        <v>0.74903500000000001</v>
+      </c>
+      <c r="C55">
+        <v>0.86494899999999997</v>
+      </c>
+      <c r="D55">
+        <v>0.84147300000000003</v>
       </c>
     </row>
   </sheetData>

--- a/测试数据.xlsx
+++ b/测试数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\F\ABlueFaceProj\20240618\Seg\Beta_BiSeNet-master_Slim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3C52647-B5AA-4931-8567-B658C8379129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A68ABC9-8850-4D09-A165-62B3E3531163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="142">
   <si>
     <t>x2</t>
   </si>
@@ -451,6 +451,14 @@
   </si>
   <si>
     <t>dinov3segnet_vit_b</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新版本</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prgseg_hgnetv2_b6</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -531,7 +539,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -548,7 +556,6 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -824,7 +831,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O55"/>
+  <dimension ref="A1:O56"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="59.109375" customWidth="1"/>
@@ -852,6 +859,9 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="9" t="s">
+        <v>140</v>
+      </c>
       <c r="I1" t="s">
         <v>4</v>
       </c>
@@ -1285,6 +1295,9 @@
       <c r="D21">
         <v>0.82219600000000004</v>
       </c>
+      <c r="E21">
+        <v>0.75261500000000003</v>
+      </c>
       <c r="F21">
         <v>0.75131099999999995</v>
       </c>
@@ -1975,7 +1988,7 @@
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A55" s="10" t="s">
+      <c r="A55" s="9" t="s">
         <v>139</v>
       </c>
       <c r="B55">
@@ -1986,6 +1999,20 @@
       </c>
       <c r="D55">
         <v>0.84147300000000003</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A56" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="B56">
+        <v>0.766594</v>
+      </c>
+      <c r="C56">
+        <v>0.88039100000000003</v>
+      </c>
+      <c r="D56">
+        <v>0.84912100000000001</v>
       </c>
     </row>
   </sheetData>

--- a/测试数据.xlsx
+++ b/测试数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\F\ABlueFaceProj\20240618\Seg\Beta_BiSeNet-master_Slim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A68ABC9-8850-4D09-A165-62B3E3531163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{965B487F-2EEB-4636-B4E4-76678BA29646}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="147">
   <si>
     <t>x2</t>
   </si>
@@ -459,6 +459,26 @@
   </si>
   <si>
     <t>prgseg_hgnetv2_b6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fastefficientbisenet_inceptionnext_atto</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.754584/0.760426</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.772044/0.777559</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fastefficientbisenet_inceptionnext_tiny</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fastefficientbisenet_inceptionnext_tiny_pro</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -539,7 +559,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -552,10 +572,25 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -831,1196 +866,1289 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O56"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="59.109375" customWidth="1"/>
-    <col min="2" max="2" width="15.109375" customWidth="1"/>
+    <col min="1" max="1" width="46.88671875" customWidth="1"/>
+    <col min="2" max="2" width="11.77734375" customWidth="1"/>
     <col min="3" max="3" width="10.88671875" customWidth="1"/>
     <col min="4" max="4" width="10.44140625" customWidth="1"/>
-    <col min="6" max="8" width="9.6640625"/>
-    <col min="9" max="9" width="11.44140625" customWidth="1"/>
-    <col min="10" max="11" width="9.6640625"/>
+    <col min="5" max="5" width="9.88671875" customWidth="1"/>
+    <col min="6" max="6" width="9.6640625"/>
+    <col min="7" max="7" width="22.44140625" customWidth="1"/>
+    <col min="8" max="8" width="9.6640625"/>
+    <col min="9" max="9" width="9.109375" customWidth="1"/>
+    <col min="11" max="11" width="17.88671875" customWidth="1"/>
     <col min="12" max="12" width="15.21875" customWidth="1"/>
-    <col min="13" max="13" width="13.44140625" customWidth="1"/>
-    <col min="14" max="14" width="22.33203125" customWidth="1"/>
+    <col min="13" max="13" width="12.33203125" customWidth="1"/>
+    <col min="14" max="14" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="I1" t="s">
+      <c r="F1" s="1">
+        <v>6</v>
+      </c>
+      <c r="G1" s="1">
+        <v>8</v>
+      </c>
+      <c r="H1" s="1">
+        <v>9</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="K1" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="L1" s="6" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="M1" s="6"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="1">
         <v>0.77989699999999995</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="1">
         <v>0.89335799999999999</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
         <v>0.85520099999999999</v>
       </c>
-      <c r="F2">
+      <c r="E2" s="1"/>
+      <c r="F2" s="1">
         <v>0.78461199999999998</v>
       </c>
-      <c r="G2">
-        <v>0.89091500000000001</v>
-      </c>
-      <c r="H2">
-        <v>0.86289400000000005</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="1">
         <v>0.77761400000000003</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>0.88759200000000005</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>0.85787100000000005</v>
       </c>
-      <c r="F3">
+      <c r="E3" s="1"/>
+      <c r="F3" s="1">
         <v>0.79134499999999997</v>
       </c>
-      <c r="G3">
-        <v>0.89273899999999995</v>
-      </c>
-      <c r="H3">
-        <v>0.86963800000000002</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="1">
         <v>0.77242900000000003</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>0.89129499999999995</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>0.84928499999999996</v>
       </c>
-      <c r="I4">
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1">
         <v>124</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="1">
         <v>0.770065</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>0.88427999999999995</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>0.85091300000000003</v>
       </c>
-      <c r="F5">
+      <c r="E5" s="1"/>
+      <c r="F5" s="1">
         <v>0.76847900000000002</v>
       </c>
-      <c r="G5">
-        <v>0.86373599999999995</v>
-      </c>
-      <c r="H5">
-        <v>0.86833300000000002</v>
-      </c>
-      <c r="I5">
+      <c r="G5" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0.76789700000000005</v>
+      </c>
+      <c r="I5" s="1">
         <v>49</v>
       </c>
-      <c r="J5">
-        <v>0.77204399999999995</v>
-      </c>
       <c r="K5">
-        <v>0.88118799999999997</v>
-      </c>
-      <c r="L5">
-        <v>0.85651299999999997</v>
-      </c>
-      <c r="N5">
         <v>1.4411799999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="1">
         <v>0.76773199999999997</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="1">
         <v>0.87141900000000005</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <v>0.86139500000000002</v>
       </c>
-      <c r="F6">
+      <c r="E6" s="1"/>
+      <c r="F6" s="1">
         <v>0.77103999999999995</v>
       </c>
-      <c r="G6">
-        <v>0.86763100000000004</v>
-      </c>
-      <c r="H6">
-        <v>0.86818799999999996</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="B7" s="1">
+        <v>0.766594</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.88039100000000003</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0.84912100000000001</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1">
+        <v>0.77905599999999997</v>
+      </c>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B7">
+      <c r="B8" s="1">
         <v>0.76629499999999995</v>
       </c>
-      <c r="C7">
+      <c r="C8" s="1">
         <v>0.88547200000000004</v>
       </c>
-      <c r="D7">
+      <c r="D8" s="1">
         <v>0.84465999999999997</v>
       </c>
-      <c r="F7">
+      <c r="E8" s="1"/>
+      <c r="F8" s="1">
         <v>0.77436899999999997</v>
       </c>
-      <c r="G7">
-        <v>0.89326300000000003</v>
-      </c>
-      <c r="H7">
-        <v>0.84846699999999997</v>
-      </c>
-      <c r="I7">
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1">
         <v>85.6</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B8">
+      <c r="B9" s="1">
         <v>0.76426000000000005</v>
       </c>
-      <c r="C8">
+      <c r="C9" s="1">
         <v>0.88559200000000005</v>
       </c>
-      <c r="D8">
+      <c r="D9" s="1">
         <v>0.84231500000000004</v>
       </c>
-      <c r="I8">
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1">
         <v>58.84</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B9">
+      <c r="B10" s="1">
         <v>0.76256900000000005</v>
       </c>
-      <c r="C9">
+      <c r="C10" s="1">
         <v>0.88412100000000005</v>
       </c>
-      <c r="D9">
+      <c r="D10" s="1">
         <v>0.84111400000000003</v>
       </c>
-      <c r="I9">
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1">
         <v>115</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B10">
+      <c r="B11" s="1">
         <v>0.76244999999999996</v>
       </c>
-      <c r="C10">
+      <c r="C11" s="1">
         <v>0.88131199999999998</v>
       </c>
-      <c r="D10">
+      <c r="D11" s="1">
         <v>0.84433000000000002</v>
       </c>
-      <c r="I10">
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1">
         <v>113</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B11">
+      <c r="B12" s="1">
         <v>0.76091900000000001</v>
       </c>
-      <c r="C11">
+      <c r="C12" s="1">
         <v>0.87430300000000005</v>
       </c>
-      <c r="D11">
+      <c r="D12" s="1">
         <v>0.84851699999999997</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B12">
+      <c r="B13" s="1">
         <v>0.76035600000000003</v>
       </c>
-      <c r="C12">
+      <c r="C13" s="1">
         <v>0.88488699999999998</v>
       </c>
-      <c r="D12">
+      <c r="D13" s="1">
         <v>0.83660800000000002</v>
       </c>
-      <c r="F12">
+      <c r="E13" s="1"/>
+      <c r="F13" s="1">
         <v>0.76341099999999995</v>
       </c>
-      <c r="G12">
-        <v>0.89001699999999995</v>
-      </c>
-      <c r="H12">
-        <v>0.83723499999999995</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B13">
+      <c r="B14" s="1">
         <v>0.75666599999999995</v>
       </c>
-      <c r="C13">
+      <c r="C14" s="1">
         <v>0.88330500000000001</v>
       </c>
-      <c r="D13">
+      <c r="D14" s="1">
         <v>0.83460699999999999</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B14">
+      <c r="B15" s="1">
         <v>0.75477700000000003</v>
       </c>
-      <c r="C14">
+      <c r="C15" s="1">
         <v>0.863089</v>
       </c>
-      <c r="D14">
+      <c r="D15" s="1">
         <v>0.85082599999999997</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B15">
+      <c r="B16" s="1">
         <v>0.75433399999999995</v>
       </c>
-      <c r="C15">
+      <c r="C16" s="1">
         <v>0.873749</v>
       </c>
-      <c r="D15">
+      <c r="D16" s="1">
         <v>0.84041299999999997</v>
       </c>
-      <c r="F15">
+      <c r="E16" s="1"/>
+      <c r="F16" s="1">
         <v>0.75883900000000004</v>
       </c>
-      <c r="G15">
-        <v>0.86963000000000001</v>
-      </c>
-      <c r="H15">
-        <v>0.84927200000000003</v>
-      </c>
-      <c r="I15">
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1">
         <v>69.849999999999994</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+    <row r="17" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B16">
+      <c r="B17" s="1">
         <v>0.75273599999999996</v>
       </c>
-      <c r="C16">
+      <c r="C17" s="1">
         <v>0.88347399999999998</v>
       </c>
-      <c r="D16">
+      <c r="D17" s="1">
         <v>0.82959099999999997</v>
       </c>
-    </row>
-    <row r="17" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B17">
+      <c r="B18" s="1">
         <v>0.75112999999999996</v>
       </c>
-      <c r="C17">
+      <c r="C18" s="1">
         <v>0.88185500000000006</v>
       </c>
-      <c r="D17">
+      <c r="D18" s="1">
         <v>0.82863299999999995</v>
       </c>
-      <c r="F17">
+      <c r="E18" s="1"/>
+      <c r="F18" s="1">
         <v>0.75516300000000003</v>
       </c>
-      <c r="G17">
-        <v>0.87317900000000004</v>
-      </c>
-      <c r="H17">
-        <v>0.84089100000000006</v>
-      </c>
-      <c r="I17">
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1">
         <v>31.4</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B18">
+      <c r="B19" s="1">
         <v>0.74993100000000001</v>
       </c>
-      <c r="C18">
+      <c r="C19" s="1">
         <v>0.88971900000000004</v>
       </c>
-      <c r="D18">
+      <c r="D19" s="1">
         <v>0.82317799999999997</v>
       </c>
-      <c r="F18">
+      <c r="E19" s="1"/>
+      <c r="F19" s="1">
         <v>0.75429500000000005</v>
       </c>
-      <c r="G18">
-        <v>0.86771600000000004</v>
-      </c>
-      <c r="H18">
-        <v>0.84682100000000005</v>
-      </c>
-      <c r="I18">
+      <c r="G19" s="1">
+        <v>0.75837500000000002</v>
+      </c>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1">
         <v>21.2</v>
       </c>
-      <c r="J18">
-        <v>0.75837500000000002</v>
-      </c>
-      <c r="K18">
-        <v>0.88571699999999998</v>
-      </c>
-      <c r="L18">
-        <v>0.83616599999999996</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="B20" s="1">
+        <v>0.74903500000000001</v>
+      </c>
+      <c r="C20" s="1">
+        <v>0.86494899999999997</v>
+      </c>
+      <c r="D20" s="1">
+        <v>0.84147300000000003</v>
+      </c>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B19">
+      <c r="B21" s="1">
         <v>0.74761</v>
       </c>
-      <c r="C19">
+      <c r="C21" s="1">
         <v>0.864012</v>
       </c>
-      <c r="D19">
+      <c r="D21" s="1">
         <v>0.84015300000000004</v>
       </c>
-      <c r="F19">
+      <c r="E21" s="1"/>
+      <c r="F21" s="1">
         <v>0.74314100000000005</v>
       </c>
-      <c r="G19">
-        <v>0.87060499999999996</v>
-      </c>
-      <c r="H19">
-        <v>0.82750800000000002</v>
-      </c>
-      <c r="I19">
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1">
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="B22" s="1">
+        <v>0.74725900000000001</v>
+      </c>
+      <c r="C22" s="1">
+        <v>0.86913899999999999</v>
+      </c>
+      <c r="D22" s="1">
+        <v>0.835422</v>
+      </c>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="K22">
+        <v>3.6217100000000002</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B20">
+      <c r="B23" s="1">
         <v>0.74657700000000005</v>
       </c>
-      <c r="C20">
+      <c r="C23" s="1">
         <v>0.86698200000000003</v>
       </c>
-      <c r="D20">
+      <c r="D23" s="1">
         <v>0.836866</v>
       </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="B24" s="1">
+        <v>0.74578599999999995</v>
+      </c>
+      <c r="C24" s="1">
+        <v>0.87922</v>
+      </c>
+      <c r="D24" s="1">
+        <v>0.82449899999999998</v>
+      </c>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1">
+        <v>0.74951400000000001</v>
+      </c>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="B25" s="1">
+        <v>0.74468699999999999</v>
+      </c>
+      <c r="C25" s="1">
+        <v>0.88054699999999997</v>
+      </c>
+      <c r="D25" s="1">
+        <v>0.82219600000000004</v>
+      </c>
+      <c r="E25" s="1">
+        <v>0.75261500000000003</v>
+      </c>
+      <c r="F25" s="1">
+        <v>0.75131099999999995</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="H25" s="1">
+        <v>0.76078100000000004</v>
+      </c>
+      <c r="I25" s="1">
+        <v>14.5</v>
+      </c>
+      <c r="K25">
+        <v>0.75868000000000002</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" s="1">
+        <v>0.74462200000000001</v>
+      </c>
+      <c r="C26" s="1">
+        <v>0.87063699999999999</v>
+      </c>
+      <c r="D26" s="1">
+        <v>0.83057499999999995</v>
+      </c>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1">
+        <v>88.3</v>
+      </c>
+      <c r="L26">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="10">
+        <v>0.744506</v>
+      </c>
+      <c r="C27" s="10">
+        <v>0.86052799999999996</v>
+      </c>
+      <c r="D27" s="10">
+        <v>0.83985100000000001</v>
+      </c>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10">
+        <v>0.75157399999999996</v>
+      </c>
+      <c r="G27" s="1"/>
+      <c r="H27" s="10"/>
+      <c r="I27" s="10">
+        <v>57.3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" s="1">
+        <v>0.74432399999999999</v>
+      </c>
+      <c r="C28" s="1">
+        <v>0.88753000000000004</v>
+      </c>
+      <c r="D28" s="1">
+        <v>0.81701400000000002</v>
+      </c>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" s="1">
+        <v>0.743591</v>
+      </c>
+      <c r="C29" s="1">
+        <v>0.872448</v>
+      </c>
+      <c r="D29" s="1">
+        <v>0.82741100000000001</v>
+      </c>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30" s="1">
+        <v>0.74173299999999998</v>
+      </c>
+      <c r="C30" s="1">
+        <v>0.86497599999999997</v>
+      </c>
+      <c r="D30" s="1">
+        <v>0.83116299999999999</v>
+      </c>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1">
+        <v>0.745726</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0.75325799999999998</v>
+      </c>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1">
+        <v>30.7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31" s="1">
+        <v>0.74162899999999998</v>
+      </c>
+      <c r="C31" s="1">
+        <v>0.86836000000000002</v>
+      </c>
+      <c r="D31" s="1">
+        <v>0.82718199999999997</v>
+      </c>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32" s="1">
+        <v>0.740506</v>
+      </c>
+      <c r="C32" s="1">
+        <v>0.865591</v>
+      </c>
+      <c r="D32" s="1">
+        <v>0.82916100000000004</v>
+      </c>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1">
+        <v>0.75195400000000001</v>
+      </c>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1">
+        <v>50.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33" s="1">
+        <v>0.73980500000000005</v>
+      </c>
+      <c r="C33" s="1">
+        <v>0.86816499999999996</v>
+      </c>
+      <c r="D33" s="1">
+        <v>0.82677999999999996</v>
+      </c>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B34" s="1">
+        <v>0.73975500000000005</v>
+      </c>
+      <c r="C34" s="1">
+        <v>0.85670999999999997</v>
+      </c>
+      <c r="D34" s="1">
+        <v>0.83675999999999995</v>
+      </c>
+      <c r="E34" s="1">
+        <v>0.74752300000000005</v>
+      </c>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1">
+        <v>0.74913600000000002</v>
+      </c>
+      <c r="H34" s="1">
+        <v>0.75407299999999999</v>
+      </c>
+      <c r="I34" s="1">
+        <v>17.97</v>
+      </c>
+      <c r="K34">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35" s="1">
+        <v>0.73849100000000001</v>
+      </c>
+      <c r="C35" s="1">
+        <v>0.86501799999999995</v>
+      </c>
+      <c r="D35" s="1">
+        <v>0.827704</v>
+      </c>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1">
+        <v>0.74363000000000001</v>
+      </c>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="1">
+        <v>0.73821400000000004</v>
+      </c>
+      <c r="C36" s="1">
+        <v>0.86428000000000005</v>
+      </c>
+      <c r="D36" s="1">
+        <v>0.82671399999999995</v>
+      </c>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="1">
+        <v>0.73571799999999998</v>
+      </c>
+      <c r="C37" s="1">
+        <v>0.87732399999999999</v>
+      </c>
+      <c r="D37" s="1">
+        <v>0.81230599999999997</v>
+      </c>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1">
+        <v>16.73</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B38" s="1">
+        <v>0.73497599999999996</v>
+      </c>
+      <c r="C38" s="1">
+        <v>0.86321599999999998</v>
+      </c>
+      <c r="D38" s="1">
+        <v>0.82403800000000005</v>
+      </c>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1">
+        <v>0.74550499999999997</v>
+      </c>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="1">
+        <v>0.73430099999999998</v>
+      </c>
+      <c r="C39" s="1">
+        <v>0.87199099999999996</v>
+      </c>
+      <c r="D39" s="1">
+        <v>0.81632199999999999</v>
+      </c>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1">
+        <v>0.75073900000000005</v>
+      </c>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="1">
+        <v>0.73252300000000004</v>
+      </c>
+      <c r="C40" s="1">
+        <v>0.86758900000000005</v>
+      </c>
+      <c r="D40" s="1">
+        <v>0.81816699999999998</v>
+      </c>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="1">
+        <v>0.73216400000000004</v>
+      </c>
+      <c r="C41" s="1">
+        <v>0.86068100000000003</v>
+      </c>
+      <c r="D41" s="1">
+        <v>0.82388899999999998</v>
+      </c>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" s="1">
+        <v>0.73082899999999995</v>
+      </c>
+      <c r="C42" s="1">
+        <v>0.86943099999999995</v>
+      </c>
+      <c r="D42" s="1">
+        <v>0.81454800000000005</v>
+      </c>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B43" s="1">
+        <v>0.72680400000000001</v>
+      </c>
+      <c r="C43" s="1">
+        <v>0.857101</v>
+      </c>
+      <c r="D43" s="1">
+        <v>0.81938500000000003</v>
+      </c>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1">
         <v>25</v>
       </c>
-      <c r="B21">
-        <v>0.74468699999999999</v>
-      </c>
-      <c r="C21">
-        <v>0.88054699999999997</v>
-      </c>
-      <c r="D21">
-        <v>0.82219600000000004</v>
-      </c>
-      <c r="E21">
-        <v>0.75261500000000003</v>
-      </c>
-      <c r="F21">
-        <v>0.75131099999999995</v>
-      </c>
-      <c r="G21">
-        <v>0.88209899999999997</v>
-      </c>
-      <c r="H21">
-        <v>0.83011900000000005</v>
-      </c>
-      <c r="I21">
-        <v>14.5</v>
-      </c>
-      <c r="J21">
-        <v>0.75458400000000003</v>
-      </c>
-      <c r="K21">
-        <v>0.87913799999999998</v>
-      </c>
-      <c r="L21">
-        <v>0.836511</v>
-      </c>
-      <c r="N21">
-        <v>0.75868000000000002</v>
-      </c>
-      <c r="O21">
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B44" s="1">
+        <v>0.72399400000000003</v>
+      </c>
+      <c r="C44" s="1">
+        <v>0.85761799999999999</v>
+      </c>
+      <c r="D44" s="1">
+        <v>0.81521999999999994</v>
+      </c>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B45" s="1">
+        <v>0.72123300000000001</v>
+      </c>
+      <c r="C45" s="1">
+        <v>0.85792599999999997</v>
+      </c>
+      <c r="D45" s="1">
+        <v>0.81019799999999997</v>
+      </c>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1">
+        <v>0.73479399999999995</v>
+      </c>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1">
+        <v>11.42</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B46" s="1">
+        <v>0.71946500000000002</v>
+      </c>
+      <c r="C46" s="1">
+        <v>0.86807000000000001</v>
+      </c>
+      <c r="D46" s="1">
+        <v>0.80044899999999997</v>
+      </c>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B47" s="1">
+        <v>0.71696099999999996</v>
+      </c>
+      <c r="C47" s="1">
+        <v>0.870251</v>
+      </c>
+      <c r="D47" s="1">
+        <v>0.79447199999999996</v>
+      </c>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B48" s="1">
+        <v>0.71694000000000002</v>
+      </c>
+      <c r="C48" s="1">
+        <v>0.86188799999999999</v>
+      </c>
+      <c r="D48" s="1">
+        <v>0.80137999999999998</v>
+      </c>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A49" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B49" s="1">
+        <v>0.71636500000000003</v>
+      </c>
+      <c r="C49" s="1">
+        <v>0.85087000000000002</v>
+      </c>
+      <c r="D49" s="1">
+        <v>0.81111999999999995</v>
+      </c>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1">
+        <v>0.73605299999999996</v>
+      </c>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1">
+        <v>7.71</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B50" s="1">
+        <v>0.71354600000000001</v>
+      </c>
+      <c r="C50" s="1">
+        <v>0.869784</v>
+      </c>
+      <c r="D50" s="1">
+        <v>0.79198400000000002</v>
+      </c>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B51" s="1">
+        <v>0.71179099999999995</v>
+      </c>
+      <c r="C51" s="1">
+        <v>0.86646400000000001</v>
+      </c>
+      <c r="D51" s="1">
+        <v>0.79112199999999999</v>
+      </c>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B52" s="1">
+        <v>0.711113</v>
+      </c>
+      <c r="C52" s="1">
+        <v>0.84625399999999995</v>
+      </c>
+      <c r="D52" s="1">
+        <v>0.806975</v>
+      </c>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B53" s="1">
+        <v>0.71059899999999998</v>
+      </c>
+      <c r="C53" s="1">
+        <v>0.86808399999999997</v>
+      </c>
+      <c r="D53" s="1">
+        <v>0.78952599999999995</v>
+      </c>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1">
+        <v>0.71683799999999998</v>
+      </c>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1">
+        <v>25</v>
+      </c>
+      <c r="L53">
         <v>0.35229700000000003</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22">
-        <v>0.74462200000000001</v>
-      </c>
-      <c r="C22">
-        <v>0.87063699999999999</v>
-      </c>
-      <c r="D22">
-        <v>0.83057499999999995</v>
-      </c>
-      <c r="I22">
-        <v>88.3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23" s="4">
-        <v>0.744506</v>
-      </c>
-      <c r="C23" s="4">
-        <v>0.86052799999999996</v>
-      </c>
-      <c r="D23" s="4">
-        <v>0.83985100000000001</v>
-      </c>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4">
-        <v>0.75157399999999996</v>
-      </c>
-      <c r="G23" s="4">
-        <v>0.86825699999999995</v>
-      </c>
-      <c r="H23" s="4">
-        <v>0.84174099999999996</v>
-      </c>
-      <c r="I23" s="4">
-        <v>57.3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>28</v>
-      </c>
-      <c r="B24">
-        <v>0.74432399999999999</v>
-      </c>
-      <c r="C24">
-        <v>0.88753000000000004</v>
-      </c>
-      <c r="D24">
-        <v>0.81701400000000002</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>29</v>
-      </c>
-      <c r="B25">
-        <v>0.743591</v>
-      </c>
-      <c r="C25">
-        <v>0.872448</v>
-      </c>
-      <c r="D25">
-        <v>0.82741100000000001</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B26">
-        <v>0.74173299999999998</v>
-      </c>
-      <c r="C26">
-        <v>0.86497599999999997</v>
-      </c>
-      <c r="D26">
-        <v>0.83116299999999999</v>
-      </c>
-      <c r="F26">
-        <v>0.745726</v>
-      </c>
-      <c r="G26">
-        <v>0.85971900000000001</v>
-      </c>
-      <c r="H26">
-        <v>0.84069199999999999</v>
-      </c>
-      <c r="I26">
-        <v>30.7</v>
-      </c>
-      <c r="J26">
-        <v>0.75325799999999998</v>
-      </c>
-      <c r="K26">
-        <v>0.86073</v>
-      </c>
-      <c r="L26">
-        <v>0.85052700000000003</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>31</v>
-      </c>
-      <c r="B27">
-        <v>0.74162899999999998</v>
-      </c>
-      <c r="C27">
-        <v>0.86836000000000002</v>
-      </c>
-      <c r="D27">
-        <v>0.82718199999999997</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>32</v>
-      </c>
-      <c r="B28">
-        <v>0.740506</v>
-      </c>
-      <c r="C28">
-        <v>0.865591</v>
-      </c>
-      <c r="D28">
-        <v>0.82916100000000004</v>
-      </c>
-      <c r="F28">
-        <v>0.75195400000000001</v>
-      </c>
-      <c r="G28">
-        <v>0.86931199999999997</v>
-      </c>
-      <c r="H28">
-        <v>0.84161600000000003</v>
-      </c>
-      <c r="I28">
-        <v>50.5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>33</v>
-      </c>
-      <c r="B29">
-        <v>0.73980500000000005</v>
-      </c>
-      <c r="C29">
-        <v>0.86816499999999996</v>
-      </c>
-      <c r="D29">
-        <v>0.82677999999999996</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30">
-        <v>0.73975500000000005</v>
-      </c>
-      <c r="C30">
-        <v>0.85670999999999997</v>
-      </c>
-      <c r="D30">
-        <v>0.83675999999999995</v>
-      </c>
-      <c r="I30">
-        <v>17.97</v>
-      </c>
-      <c r="J30">
-        <v>0.74913600000000002</v>
-      </c>
-      <c r="K30">
-        <v>0.85268299999999997</v>
-      </c>
-      <c r="L30">
-        <v>0.85444900000000001</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B31">
-        <v>0.73849100000000001</v>
-      </c>
-      <c r="C31">
-        <v>0.86501799999999995</v>
-      </c>
-      <c r="D31">
-        <v>0.827704</v>
-      </c>
-      <c r="F31">
-        <v>0.74363000000000001</v>
-      </c>
-      <c r="G31">
-        <v>0.85514400000000002</v>
-      </c>
-      <c r="H31">
-        <v>0.84365900000000005</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="M31">
-        <v>30.6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32">
-        <v>0.73821400000000004</v>
-      </c>
-      <c r="C32">
-        <v>0.86428000000000005</v>
-      </c>
-      <c r="D32">
-        <v>0.82671399999999995</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33">
-        <v>0.73571799999999998</v>
-      </c>
-      <c r="C33">
-        <v>0.87732399999999999</v>
-      </c>
-      <c r="D33">
-        <v>0.81230599999999997</v>
-      </c>
-      <c r="I33">
-        <v>16.73</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34">
-        <v>0.73430099999999998</v>
-      </c>
-      <c r="C34">
-        <v>0.87199099999999996</v>
-      </c>
-      <c r="D34">
-        <v>0.81632199999999999</v>
-      </c>
-      <c r="I34">
-        <v>31</v>
-      </c>
-      <c r="J34">
-        <v>0.75073900000000005</v>
-      </c>
-      <c r="K34">
-        <v>0.87304700000000002</v>
-      </c>
-      <c r="L34">
-        <v>0.83609699999999998</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35">
-        <v>0.73252300000000004</v>
-      </c>
-      <c r="C35">
-        <v>0.86758900000000005</v>
-      </c>
-      <c r="D35">
-        <v>0.81816699999999998</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36">
-        <v>0.73216400000000004</v>
-      </c>
-      <c r="C36">
-        <v>0.86068100000000003</v>
-      </c>
-      <c r="D36">
-        <v>0.82388899999999998</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>42</v>
-      </c>
-      <c r="B37">
-        <v>0.73082899999999995</v>
-      </c>
-      <c r="C37">
-        <v>0.86943099999999995</v>
-      </c>
-      <c r="D37">
-        <v>0.81454800000000005</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>43</v>
-      </c>
-      <c r="B38">
-        <v>0.72680400000000001</v>
-      </c>
-      <c r="C38">
-        <v>0.857101</v>
-      </c>
-      <c r="D38">
-        <v>0.81938500000000003</v>
-      </c>
-      <c r="I38">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>44</v>
-      </c>
-      <c r="B39">
-        <v>0.72399400000000003</v>
-      </c>
-      <c r="C39">
-        <v>0.85761799999999999</v>
-      </c>
-      <c r="D39">
-        <v>0.81521999999999994</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>45</v>
-      </c>
-      <c r="B40">
-        <v>0.71946500000000002</v>
-      </c>
-      <c r="C40">
-        <v>0.86807000000000001</v>
-      </c>
-      <c r="D40">
-        <v>0.80044899999999997</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>46</v>
-      </c>
-      <c r="B41">
-        <v>0.71696099999999996</v>
-      </c>
-      <c r="C41">
-        <v>0.870251</v>
-      </c>
-      <c r="D41">
-        <v>0.79447199999999996</v>
-      </c>
-      <c r="I41">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>47</v>
-      </c>
-      <c r="B42">
-        <v>0.71694000000000002</v>
-      </c>
-      <c r="C42">
-        <v>0.86188799999999999</v>
-      </c>
-      <c r="D42">
-        <v>0.80137999999999998</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A43" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B43">
-        <v>0.71636500000000003</v>
-      </c>
-      <c r="C43">
-        <v>0.85087000000000002</v>
-      </c>
-      <c r="D43">
-        <v>0.81111999999999995</v>
-      </c>
-      <c r="I43">
-        <v>7.71</v>
-      </c>
-      <c r="J43">
-        <v>0.73605299999999996</v>
-      </c>
-      <c r="K43">
-        <v>0.85793399999999997</v>
-      </c>
-      <c r="L43">
-        <v>0.83193700000000004</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>49</v>
-      </c>
-      <c r="B44">
-        <v>0.71354600000000001</v>
-      </c>
-      <c r="C44">
-        <v>0.869784</v>
-      </c>
-      <c r="D44">
-        <v>0.79198400000000002</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>50</v>
-      </c>
-      <c r="B45">
-        <v>0.71179099999999995</v>
-      </c>
-      <c r="C45">
-        <v>0.86646400000000001</v>
-      </c>
-      <c r="D45">
-        <v>0.79112199999999999</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>51</v>
-      </c>
-      <c r="B46">
-        <v>0.711113</v>
-      </c>
-      <c r="C46">
-        <v>0.84625399999999995</v>
-      </c>
-      <c r="D46">
-        <v>0.806975</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A47" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B47">
-        <v>0.71059899999999998</v>
-      </c>
-      <c r="C47">
-        <v>0.86808399999999997</v>
-      </c>
-      <c r="D47">
-        <v>0.78952599999999995</v>
-      </c>
-      <c r="I47">
-        <v>25</v>
-      </c>
-      <c r="J47">
-        <v>0.71683799999999998</v>
-      </c>
-      <c r="K47">
-        <v>0.848993</v>
-      </c>
-      <c r="L47">
-        <v>0.81343399999999999</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A48" s="6" t="s">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A54" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="B48">
+      <c r="B54" s="1">
         <v>0.69976499999999997</v>
       </c>
-      <c r="C48">
+      <c r="C54" s="1">
         <v>0.84911899999999996</v>
       </c>
-      <c r="D48">
+      <c r="D54" s="1">
         <v>0.788358</v>
       </c>
-      <c r="F48">
+      <c r="E54" s="1"/>
+      <c r="F54" s="1">
         <v>0.69891499999999995</v>
       </c>
-      <c r="G48">
-        <v>0.847132</v>
-      </c>
-      <c r="H48">
-        <v>0.78894299999999995</v>
-      </c>
-      <c r="I48">
+      <c r="G54" s="1">
+        <v>0.71306599999999998</v>
+      </c>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1">
         <v>9.74</v>
       </c>
-      <c r="J48">
-        <v>0.71306599999999998</v>
-      </c>
-      <c r="K48">
-        <v>0.852715</v>
-      </c>
-      <c r="L48">
-        <v>0.80514799999999997</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A49" s="6" t="s">
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A55" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="B49">
+      <c r="B55" s="1">
         <v>0.69904900000000003</v>
       </c>
-      <c r="C49">
+      <c r="C55" s="1">
         <v>0.85933199999999998</v>
       </c>
-      <c r="D49">
+      <c r="D55" s="1">
         <v>0.781447</v>
       </c>
-      <c r="I49">
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1">
+        <v>0.69198599999999999</v>
+      </c>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1">
         <v>12.94</v>
       </c>
-      <c r="J49">
-        <v>0.69198599999999999</v>
-      </c>
-      <c r="K49">
-        <v>0.83943800000000002</v>
-      </c>
-      <c r="L49">
-        <v>0.78869900000000004</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B50">
+      <c r="B56" s="1">
         <v>0.69497900000000001</v>
       </c>
-      <c r="C50">
+      <c r="C56" s="1">
         <v>0.86561600000000005</v>
       </c>
-      <c r="D50">
+      <c r="D56" s="1">
         <v>0.77168300000000001</v>
       </c>
-      <c r="F50">
+      <c r="E56" s="1"/>
+      <c r="F56" s="1">
         <v>0.69739899999999999</v>
       </c>
-      <c r="G50">
-        <v>0.868533</v>
-      </c>
-      <c r="H50">
-        <v>0.771671</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A51" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B51">
-        <v>0.73497599999999996</v>
-      </c>
-      <c r="C51">
-        <v>0.86321599999999998</v>
-      </c>
-      <c r="D51">
-        <v>0.82403800000000005</v>
-      </c>
-      <c r="I51">
-        <v>22.9</v>
-      </c>
-      <c r="J51">
-        <v>0.74550499999999997</v>
-      </c>
-      <c r="K51">
-        <v>0.86067899999999997</v>
-      </c>
-      <c r="L51">
-        <v>0.84021999999999997</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A52" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B52">
-        <v>0.72123300000000001</v>
-      </c>
-      <c r="C52">
-        <v>0.85792599999999997</v>
-      </c>
-      <c r="D52">
-        <v>0.81019799999999997</v>
-      </c>
-      <c r="I52">
-        <v>11.42</v>
-      </c>
-      <c r="J52">
-        <v>0.73479399999999995</v>
-      </c>
-      <c r="K52">
-        <v>0.85729500000000003</v>
-      </c>
-      <c r="L52">
-        <v>0.83084400000000003</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A53" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="B53">
-        <v>0.74578599999999995</v>
-      </c>
-      <c r="C53">
-        <v>0.87922</v>
-      </c>
-      <c r="D53">
-        <v>0.82449899999999998</v>
-      </c>
-      <c r="J53">
-        <v>0.74951400000000001</v>
-      </c>
-      <c r="K53">
-        <v>0.88462300000000005</v>
-      </c>
-      <c r="L53">
-        <v>0.82542499999999996</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A54" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="B54">
-        <v>0.74725900000000001</v>
-      </c>
-      <c r="C54">
-        <v>0.86913899999999999</v>
-      </c>
-      <c r="D54">
-        <v>0.835422</v>
-      </c>
-      <c r="N54">
-        <v>3.6217100000000002</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A55" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="B55">
-        <v>0.74903500000000001</v>
-      </c>
-      <c r="C55">
-        <v>0.86494899999999997</v>
-      </c>
-      <c r="D55">
-        <v>0.84147300000000003</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A56" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="B56">
-        <v>0.766594</v>
-      </c>
-      <c r="C56">
-        <v>0.88039100000000003</v>
-      </c>
-      <c r="D56">
-        <v>0.84912100000000001</v>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
+    </row>
+    <row r="57" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="B57" s="1">
+        <v>0.78243600000000002</v>
+      </c>
+      <c r="C57" s="1">
+        <v>0.89274200000000004</v>
+      </c>
+      <c r="D57" s="1">
+        <v>0.85849200000000003</v>
+      </c>
+      <c r="G57" s="1">
+        <v>0.78455699999999995</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A58" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="B58" s="1">
+        <v>0.78566499999999995</v>
+      </c>
+      <c r="C58" s="1">
+        <v>0.89692000000000005</v>
+      </c>
+      <c r="D58" s="1">
+        <v>0.85882999999999998</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:L50">
-    <sortCondition descending="1" ref="B1:B50"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L58">
+    <sortCondition descending="1" ref="B2:B58"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/测试数据.xlsx
+++ b/测试数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\F\ABlueFaceProj\20240618\Seg\Beta_BiSeNet-master_Slim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{965B487F-2EEB-4636-B4E4-76678BA29646}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47E109CA-27BC-431E-9E0F-326D60D0C7EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="149">
   <si>
     <t>x2</t>
   </si>
@@ -479,6 +479,14 @@
   </si>
   <si>
     <t>fastefficientbisenet_inceptionnext_tiny_pro</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gpu512x512-new</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fastefficientbisenet_inceptionnext_tiny_pro_max</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -588,8 +596,8 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -866,7 +874,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46.88671875" customWidth="1"/>
@@ -877,7 +885,8 @@
     <col min="6" max="6" width="9.6640625"/>
     <col min="7" max="7" width="22.44140625" customWidth="1"/>
     <col min="8" max="8" width="9.6640625"/>
-    <col min="9" max="9" width="9.109375" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" customWidth="1"/>
+    <col min="10" max="10" width="19.44140625" customWidth="1"/>
     <col min="11" max="11" width="17.88671875" customWidth="1"/>
     <col min="12" max="12" width="15.21875" customWidth="1"/>
     <col min="13" max="13" width="12.33203125" customWidth="1"/>
@@ -912,6 +921,9 @@
       <c r="I1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="J1" s="7" t="s">
+        <v>147</v>
+      </c>
       <c r="K1" s="6" t="s">
         <v>137</v>
       </c>
@@ -1011,6 +1023,9 @@
       <c r="I5" s="1">
         <v>49</v>
       </c>
+      <c r="J5" s="1">
+        <v>8.86</v>
+      </c>
       <c r="K5">
         <v>1.4411799999999999</v>
       </c>
@@ -1037,7 +1052,7 @@
       <c r="I6" s="1"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="7" t="s">
         <v>141</v>
       </c>
       <c r="B7" s="1">
@@ -1443,6 +1458,9 @@
       <c r="I25" s="1">
         <v>14.5</v>
       </c>
+      <c r="J25" s="1">
+        <v>2.8</v>
+      </c>
       <c r="K25">
         <v>0.75868000000000002</v>
       </c>
@@ -2140,6 +2158,20 @@
       </c>
       <c r="D58" s="1">
         <v>0.85882999999999998</v>
+      </c>
+      <c r="G58" s="12">
+        <v>0.79378300000000002</v>
+      </c>
+      <c r="J58">
+        <v>10.67</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A59" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="J59">
+        <v>10.33</v>
       </c>
     </row>
   </sheetData>

--- a/测试数据.xlsx
+++ b/测试数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\F\ABlueFaceProj\20240618\Seg\Beta_BiSeNet-master_Slim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47E109CA-27BC-431E-9E0F-326D60D0C7EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C84E4A92-EFB0-4135-AA4A-2659163C81F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="152">
   <si>
     <t>x2</t>
   </si>
@@ -487,6 +487,18 @@
   </si>
   <si>
     <t>fastefficientbisenet_inceptionnext_tiny_pro_max</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>yolo26-n-seg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>yolo26-s-seg</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -494,7 +506,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -511,6 +523,13 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -567,7 +586,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -598,6 +617,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -872,9 +894,31 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="438" row="2">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{C8762DE7-D655-46F1-A5F6-BE6177D08F5C}">
+  <we:reference id="wa200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;71ab996e-5b39-477b-9d68-faafe8542cb4&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46.88671875" customWidth="1"/>
@@ -2170,8 +2214,43 @@
       <c r="A59" s="9" t="s">
         <v>148</v>
       </c>
+      <c r="B59">
+        <v>0.78639000000000003</v>
+      </c>
+      <c r="C59">
+        <v>0.89660399999999996</v>
+      </c>
+      <c r="D59">
+        <v>0.86029599999999995</v>
+      </c>
+      <c r="G59" s="1">
+        <v>0.78982600000000003</v>
+      </c>
       <c r="J59">
         <v>10.33</v>
+      </c>
+      <c r="K59" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A60" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="B60">
+        <v>0.71189999999999998</v>
+      </c>
+      <c r="J60">
+        <v>1.33</v>
+      </c>
+      <c r="K60" s="6"/>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A61" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="J61">
+        <v>2.65</v>
       </c>
     </row>
   </sheetData>

--- a/测试数据.xlsx
+++ b/测试数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\F\ABlueFaceProj\20240618\Seg\Beta_BiSeNet-master_Slim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C84E4A92-EFB0-4135-AA4A-2659163C81F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B34A3CFC-3ED4-4C11-87E4-B7AB66089684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,12 +22,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">小模型!$A$1:$G$37</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="144525" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="155">
   <si>
     <t>x2</t>
   </si>
@@ -499,6 +499,18 @@
   </si>
   <si>
     <t>yolo26-s-seg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fastefficientbisenet_fasternet_t0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fastefficientbisenet_fasternet_t0_reparam</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fastefficientbisenet_cpubone_nano_reparam</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -918,7 +930,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46.88671875" customWidth="1"/>
@@ -977,302 +989,310 @@
       <c r="M1" s="6"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="1">
-        <v>0.77989699999999995</v>
-      </c>
-      <c r="C2" s="1">
-        <v>0.89335799999999999</v>
-      </c>
-      <c r="D2" s="1">
-        <v>0.85520099999999999</v>
-      </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1">
-        <v>0.78461199999999998</v>
-      </c>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1" t="s">
-        <v>6</v>
+      <c r="A2" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="B2">
+        <v>0.78639000000000003</v>
+      </c>
+      <c r="C2">
+        <v>0.89660399999999996</v>
+      </c>
+      <c r="D2">
+        <v>0.86029599999999995</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.78982600000000003</v>
+      </c>
+      <c r="J2">
+        <v>10.33</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>7</v>
+      <c r="A3" s="9" t="s">
+        <v>146</v>
       </c>
       <c r="B3" s="1">
-        <v>0.77761400000000003</v>
+        <v>0.78566499999999995</v>
       </c>
       <c r="C3" s="1">
-        <v>0.88759200000000005</v>
+        <v>0.89692000000000005</v>
       </c>
       <c r="D3" s="1">
-        <v>0.85787100000000005</v>
-      </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1">
-        <v>0.79134499999999997</v>
-      </c>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
+        <v>0.85882999999999998</v>
+      </c>
+      <c r="G3" s="12">
+        <v>0.79378300000000002</v>
+      </c>
+      <c r="J3">
+        <v>10.67</v>
+      </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
+      <c r="A4" s="9" t="s">
+        <v>145</v>
       </c>
       <c r="B4" s="1">
-        <v>0.77242900000000003</v>
+        <v>0.78243600000000002</v>
       </c>
       <c r="C4" s="1">
-        <v>0.89129499999999995</v>
+        <v>0.89274200000000004</v>
       </c>
       <c r="D4" s="1">
-        <v>0.84928499999999996</v>
+        <v>0.85849200000000003</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
+      <c r="G4" s="1">
+        <v>0.78455699999999995</v>
+      </c>
       <c r="H4" s="1"/>
-      <c r="I4" s="1">
-        <v>124</v>
-      </c>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
-        <v>9</v>
+      <c r="A5" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="B5" s="1">
-        <v>0.770065</v>
+        <v>0.77989699999999995</v>
       </c>
       <c r="C5" s="1">
-        <v>0.88427999999999995</v>
+        <v>0.89335799999999999</v>
       </c>
       <c r="D5" s="1">
-        <v>0.85091300000000003</v>
+        <v>0.85520099999999999</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1">
-        <v>0.76847900000000002</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="H5" s="1">
-        <v>0.76789700000000005</v>
-      </c>
-      <c r="I5" s="1">
-        <v>49</v>
-      </c>
-      <c r="J5" s="1">
-        <v>8.86</v>
-      </c>
-      <c r="K5">
-        <v>1.4411799999999999</v>
+        <v>0.78461199999999998</v>
+      </c>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B6" s="1">
-        <v>0.76773199999999997</v>
+        <v>0.77761400000000003</v>
       </c>
       <c r="C6" s="1">
-        <v>0.87141900000000005</v>
+        <v>0.88759200000000005</v>
       </c>
       <c r="D6" s="1">
-        <v>0.86139500000000002</v>
+        <v>0.85787100000000005</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1">
-        <v>0.77103999999999995</v>
+        <v>0.79134499999999997</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>141</v>
+      <c r="A7" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="B7" s="1">
-        <v>0.766594</v>
+        <v>0.77242900000000003</v>
       </c>
       <c r="C7" s="1">
-        <v>0.88039100000000003</v>
+        <v>0.89129499999999995</v>
       </c>
       <c r="D7" s="1">
-        <v>0.84912100000000001</v>
+        <v>0.84928499999999996</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
-      <c r="G7" s="1">
-        <v>0.77905599999999997</v>
-      </c>
+      <c r="G7" s="1"/>
       <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
+      <c r="I7" s="1">
+        <v>124</v>
+      </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>11</v>
+      <c r="A8" s="8" t="s">
+        <v>9</v>
       </c>
       <c r="B8" s="1">
-        <v>0.76629499999999995</v>
+        <v>0.770065</v>
       </c>
       <c r="C8" s="1">
-        <v>0.88547200000000004</v>
+        <v>0.88427999999999995</v>
       </c>
       <c r="D8" s="1">
-        <v>0.84465999999999997</v>
+        <v>0.85091300000000003</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1">
-        <v>0.77436899999999997</v>
-      </c>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
+        <v>0.76847900000000002</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0.76789700000000005</v>
+      </c>
       <c r="I8" s="1">
-        <v>85.6</v>
+        <v>49</v>
+      </c>
+      <c r="J8" s="1">
+        <v>8.86</v>
+      </c>
+      <c r="K8">
+        <v>1.4411799999999999</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B9" s="1">
-        <v>0.76426000000000005</v>
+        <v>0.76773199999999997</v>
       </c>
       <c r="C9" s="1">
-        <v>0.88559200000000005</v>
+        <v>0.87141900000000005</v>
       </c>
       <c r="D9" s="1">
-        <v>0.84231500000000004</v>
+        <v>0.86139500000000002</v>
       </c>
       <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
+      <c r="F9" s="1">
+        <v>0.77103999999999995</v>
+      </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
-      <c r="I9" s="1">
-        <v>58.84</v>
-      </c>
+      <c r="I9" s="1"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>13</v>
+      <c r="A10" s="7" t="s">
+        <v>141</v>
       </c>
       <c r="B10" s="1">
-        <v>0.76256900000000005</v>
+        <v>0.766594</v>
       </c>
       <c r="C10" s="1">
-        <v>0.88412100000000005</v>
+        <v>0.88039100000000003</v>
       </c>
       <c r="D10" s="1">
-        <v>0.84111400000000003</v>
+        <v>0.84912100000000001</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
+      <c r="G10" s="1">
+        <v>0.77905599999999997</v>
+      </c>
       <c r="H10" s="1"/>
-      <c r="I10" s="1">
-        <v>115</v>
-      </c>
+      <c r="I10" s="1"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B11" s="1">
-        <v>0.76244999999999996</v>
+        <v>0.76629499999999995</v>
       </c>
       <c r="C11" s="1">
-        <v>0.88131199999999998</v>
+        <v>0.88547200000000004</v>
       </c>
       <c r="D11" s="1">
-        <v>0.84433000000000002</v>
+        <v>0.84465999999999997</v>
       </c>
       <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
+      <c r="F11" s="1">
+        <v>0.77436899999999997</v>
+      </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1">
-        <v>113</v>
+        <v>85.6</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B12" s="1">
-        <v>0.76091900000000001</v>
+        <v>0.76426000000000005</v>
       </c>
       <c r="C12" s="1">
-        <v>0.87430300000000005</v>
+        <v>0.88559200000000005</v>
       </c>
       <c r="D12" s="1">
-        <v>0.84851699999999997</v>
+        <v>0.84231500000000004</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
+      <c r="I12" s="1">
+        <v>58.84</v>
+      </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B13" s="1">
-        <v>0.76035600000000003</v>
+        <v>0.76256900000000005</v>
       </c>
       <c r="C13" s="1">
-        <v>0.88488699999999998</v>
+        <v>0.88412100000000005</v>
       </c>
       <c r="D13" s="1">
-        <v>0.83660800000000002</v>
+        <v>0.84111400000000003</v>
       </c>
       <c r="E13" s="1"/>
-      <c r="F13" s="1">
-        <v>0.76341099999999995</v>
-      </c>
+      <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
+      <c r="I13" s="1">
+        <v>115</v>
+      </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B14" s="1">
-        <v>0.75666599999999995</v>
+        <v>0.76244999999999996</v>
       </c>
       <c r="C14" s="1">
-        <v>0.88330500000000001</v>
+        <v>0.88131199999999998</v>
       </c>
       <c r="D14" s="1">
-        <v>0.83460699999999999</v>
+        <v>0.84433000000000002</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
+      <c r="I14" s="1">
+        <v>113</v>
+      </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B15" s="1">
-        <v>0.75477700000000003</v>
+        <v>0.76091900000000001</v>
       </c>
       <c r="C15" s="1">
-        <v>0.863089</v>
+        <v>0.87430300000000005</v>
       </c>
       <c r="D15" s="1">
-        <v>0.85082599999999997</v>
+        <v>0.84851699999999997</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
@@ -1282,39 +1302,37 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B16" s="1">
-        <v>0.75433399999999995</v>
+        <v>0.76035600000000003</v>
       </c>
       <c r="C16" s="1">
-        <v>0.873749</v>
+        <v>0.88488699999999998</v>
       </c>
       <c r="D16" s="1">
-        <v>0.84041299999999997</v>
+        <v>0.83660800000000002</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1">
-        <v>0.75883900000000004</v>
+        <v>0.76341099999999995</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
-      <c r="I16" s="1">
-        <v>69.849999999999994</v>
-      </c>
+      <c r="I16" s="1"/>
     </row>
     <row r="17" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B17" s="1">
-        <v>0.75273599999999996</v>
+        <v>0.75666599999999995</v>
       </c>
       <c r="C17" s="1">
-        <v>0.88347399999999998</v>
+        <v>0.88330500000000001</v>
       </c>
       <c r="D17" s="1">
-        <v>0.82959099999999997</v>
+        <v>0.83460699999999999</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
@@ -1323,65 +1341,59 @@
       <c r="I17" s="1"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="s">
-        <v>21</v>
+      <c r="A18" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="B18" s="1">
-        <v>0.75112999999999996</v>
+        <v>0.75477700000000003</v>
       </c>
       <c r="C18" s="1">
-        <v>0.88185500000000006</v>
+        <v>0.863089</v>
       </c>
       <c r="D18" s="1">
-        <v>0.82863299999999995</v>
+        <v>0.85082599999999997</v>
       </c>
       <c r="E18" s="1"/>
-      <c r="F18" s="1">
-        <v>0.75516300000000003</v>
-      </c>
+      <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
-      <c r="I18" s="1">
-        <v>31.4</v>
-      </c>
+      <c r="I18" s="1"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="s">
-        <v>22</v>
+      <c r="A19" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="B19" s="1">
-        <v>0.74993100000000001</v>
+        <v>0.75433399999999995</v>
       </c>
       <c r="C19" s="1">
-        <v>0.88971900000000004</v>
+        <v>0.873749</v>
       </c>
       <c r="D19" s="1">
-        <v>0.82317799999999997</v>
+        <v>0.84041299999999997</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1">
-        <v>0.75429500000000005</v>
-      </c>
-      <c r="G19" s="1">
-        <v>0.75837500000000002</v>
-      </c>
+        <v>0.75883900000000004</v>
+      </c>
+      <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1">
-        <v>21.2</v>
+        <v>69.849999999999994</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
-        <v>139</v>
+      <c r="A20" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="B20" s="1">
-        <v>0.74903500000000001</v>
+        <v>0.75273599999999996</v>
       </c>
       <c r="C20" s="1">
-        <v>0.86494899999999997</v>
+        <v>0.88347399999999998</v>
       </c>
       <c r="D20" s="1">
-        <v>0.84147300000000003</v>
+        <v>0.82959099999999997</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
@@ -1391,61 +1403,69 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B21" s="1">
-        <v>0.74761</v>
+        <v>0.75112999999999996</v>
       </c>
       <c r="C21" s="1">
-        <v>0.864012</v>
+        <v>0.88185500000000006</v>
       </c>
       <c r="D21" s="1">
-        <v>0.84015300000000004</v>
+        <v>0.82863299999999995</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1">
-        <v>0.74314100000000005</v>
+        <v>0.75516300000000003</v>
       </c>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1">
-        <v>37</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
-        <v>136</v>
+      <c r="A22" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="B22" s="1">
-        <v>0.74725900000000001</v>
+        <v>0.74993100000000001</v>
       </c>
       <c r="C22" s="1">
-        <v>0.86913899999999999</v>
+        <v>0.88971900000000004</v>
       </c>
       <c r="D22" s="1">
-        <v>0.835422</v>
+        <v>0.82317799999999997</v>
       </c>
       <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="K22">
-        <v>3.6217100000000002</v>
+      <c r="F22" s="1">
+        <v>0.75429500000000005</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0.75837500000000002</v>
+      </c>
+      <c r="H22" s="1">
+        <v>0.77152100000000001</v>
+      </c>
+      <c r="I22" s="1">
+        <v>21.2</v>
+      </c>
+      <c r="J22" s="1">
+        <v>2.9</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>24</v>
+      <c r="A23" s="7" t="s">
+        <v>139</v>
       </c>
       <c r="B23" s="1">
-        <v>0.74657700000000005</v>
+        <v>0.74903500000000001</v>
       </c>
       <c r="C23" s="1">
-        <v>0.86698200000000003</v>
+        <v>0.86494899999999997</v>
       </c>
       <c r="D23" s="1">
-        <v>0.836866</v>
+        <v>0.84147300000000003</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
@@ -1454,183 +1474,184 @@
       <c r="I23" s="1"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="9" t="s">
-        <v>135</v>
+      <c r="A24" s="8" t="s">
+        <v>23</v>
       </c>
       <c r="B24" s="1">
-        <v>0.74578599999999995</v>
+        <v>0.74761</v>
       </c>
       <c r="C24" s="1">
-        <v>0.87922</v>
+        <v>0.864012</v>
       </c>
       <c r="D24" s="1">
-        <v>0.82449899999999998</v>
+        <v>0.84015300000000004</v>
       </c>
       <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1">
-        <v>0.74951400000000001</v>
-      </c>
+      <c r="F24" s="1">
+        <v>0.74314100000000005</v>
+      </c>
+      <c r="G24" s="1"/>
       <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
+      <c r="I24" s="1">
+        <v>37</v>
+      </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="B25" s="1">
-        <v>0.74468699999999999</v>
+        <v>0.74725900000000001</v>
       </c>
       <c r="C25" s="1">
-        <v>0.88054699999999997</v>
+        <v>0.86913899999999999</v>
       </c>
       <c r="D25" s="1">
-        <v>0.82219600000000004</v>
-      </c>
-      <c r="E25" s="1">
-        <v>0.75261500000000003</v>
-      </c>
-      <c r="F25" s="1">
-        <v>0.75131099999999995</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="H25" s="1">
-        <v>0.76078100000000004</v>
-      </c>
-      <c r="I25" s="1">
-        <v>14.5</v>
-      </c>
-      <c r="J25" s="1">
-        <v>2.8</v>
-      </c>
+        <v>0.835422</v>
+      </c>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
       <c r="K25">
-        <v>0.75868000000000002</v>
+        <v>3.6217100000000002</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="s">
-        <v>26</v>
+      <c r="A26" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="B26" s="1">
-        <v>0.74462200000000001</v>
+        <v>0.74657700000000005</v>
       </c>
       <c r="C26" s="1">
-        <v>0.87063699999999999</v>
+        <v>0.86698200000000003</v>
       </c>
       <c r="D26" s="1">
-        <v>0.83057499999999995</v>
+        <v>0.836866</v>
       </c>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
-      <c r="I26" s="1">
-        <v>88.3</v>
-      </c>
-      <c r="L26">
-        <v>0.88</v>
-      </c>
+      <c r="I26" s="1"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27" s="10">
-        <v>0.744506</v>
-      </c>
-      <c r="C27" s="10">
-        <v>0.86052799999999996</v>
-      </c>
-      <c r="D27" s="10">
-        <v>0.83985100000000001</v>
-      </c>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10">
-        <v>0.75157399999999996</v>
-      </c>
-      <c r="G27" s="1"/>
-      <c r="H27" s="10"/>
-      <c r="I27" s="10">
-        <v>57.3</v>
-      </c>
+      <c r="A27" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="B27" s="1">
+        <v>0.74578599999999995</v>
+      </c>
+      <c r="C27" s="1">
+        <v>0.87922</v>
+      </c>
+      <c r="D27" s="1">
+        <v>0.82449899999999998</v>
+      </c>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1">
+        <v>0.74951400000000001</v>
+      </c>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>28</v>
+      <c r="A28" s="9" t="s">
+        <v>142</v>
       </c>
       <c r="B28" s="1">
-        <v>0.74432399999999999</v>
+        <v>0.74468699999999999</v>
       </c>
       <c r="C28" s="1">
-        <v>0.88753000000000004</v>
+        <v>0.88054699999999997</v>
       </c>
       <c r="D28" s="1">
-        <v>0.81701400000000002</v>
-      </c>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
+        <v>0.82219600000000004</v>
+      </c>
+      <c r="E28" s="1">
+        <v>0.75261500000000003</v>
+      </c>
+      <c r="F28" s="1">
+        <v>0.75131099999999995</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="H28" s="1">
+        <v>0.76078100000000004</v>
+      </c>
+      <c r="I28" s="1">
+        <v>14.5</v>
+      </c>
+      <c r="J28" s="1">
+        <v>2.8</v>
+      </c>
+      <c r="K28">
+        <v>0.75868000000000002</v>
+      </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>29</v>
+      <c r="A29" s="8" t="s">
+        <v>26</v>
       </c>
       <c r="B29" s="1">
-        <v>0.743591</v>
+        <v>0.74462200000000001</v>
       </c>
       <c r="C29" s="1">
-        <v>0.872448</v>
+        <v>0.87063699999999999</v>
       </c>
       <c r="D29" s="1">
-        <v>0.82741100000000001</v>
+        <v>0.83057499999999995</v>
       </c>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
+      <c r="I29" s="1">
+        <v>88.3</v>
+      </c>
+      <c r="L29">
+        <v>0.88</v>
+      </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30" s="1">
-        <v>0.74173299999999998</v>
-      </c>
-      <c r="C30" s="1">
-        <v>0.86497599999999997</v>
-      </c>
-      <c r="D30" s="1">
-        <v>0.83116299999999999</v>
-      </c>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1">
-        <v>0.745726</v>
-      </c>
-      <c r="G30" s="1">
-        <v>0.75325799999999998</v>
-      </c>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1">
-        <v>30.7</v>
+      <c r="A30" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" s="10">
+        <v>0.744506</v>
+      </c>
+      <c r="C30" s="10">
+        <v>0.86052799999999996</v>
+      </c>
+      <c r="D30" s="10">
+        <v>0.83985100000000001</v>
+      </c>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10">
+        <v>0.75157399999999996</v>
+      </c>
+      <c r="G30" s="1"/>
+      <c r="H30" s="10"/>
+      <c r="I30" s="10">
+        <v>57.3</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B31" s="1">
-        <v>0.74162899999999998</v>
+        <v>0.74432399999999999</v>
       </c>
       <c r="C31" s="1">
-        <v>0.86836000000000002</v>
+        <v>0.88753000000000004</v>
       </c>
       <c r="D31" s="1">
-        <v>0.82718199999999997</v>
+        <v>0.81701400000000002</v>
       </c>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
@@ -1640,111 +1661,102 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B32" s="1">
-        <v>0.740506</v>
+        <v>0.743591</v>
       </c>
       <c r="C32" s="1">
-        <v>0.865591</v>
+        <v>0.872448</v>
       </c>
       <c r="D32" s="1">
-        <v>0.82916100000000004</v>
+        <v>0.82741100000000001</v>
       </c>
       <c r="E32" s="1"/>
-      <c r="F32" s="1">
-        <v>0.75195400000000001</v>
-      </c>
+      <c r="F32" s="1"/>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
-      <c r="I32" s="1">
-        <v>50.5</v>
-      </c>
+      <c r="I32" s="1"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>33</v>
+      <c r="A33" s="8" t="s">
+        <v>30</v>
       </c>
       <c r="B33" s="1">
-        <v>0.73980500000000005</v>
+        <v>0.74173299999999998</v>
       </c>
       <c r="C33" s="1">
-        <v>0.86816499999999996</v>
+        <v>0.86497599999999997</v>
       </c>
       <c r="D33" s="1">
-        <v>0.82677999999999996</v>
+        <v>0.83116299999999999</v>
       </c>
       <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
+      <c r="F33" s="1">
+        <v>0.745726</v>
+      </c>
+      <c r="G33" s="1">
+        <v>0.75325799999999998</v>
+      </c>
       <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
+      <c r="I33" s="1">
+        <v>30.7</v>
+      </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="8" t="s">
-        <v>34</v>
+      <c r="A34" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="B34" s="1">
-        <v>0.73975500000000005</v>
+        <v>0.74162899999999998</v>
       </c>
       <c r="C34" s="1">
-        <v>0.85670999999999997</v>
+        <v>0.86836000000000002</v>
       </c>
       <c r="D34" s="1">
-        <v>0.83675999999999995</v>
-      </c>
-      <c r="E34" s="1">
-        <v>0.74752300000000005</v>
-      </c>
+        <v>0.82718199999999997</v>
+      </c>
+      <c r="E34" s="1"/>
       <c r="F34" s="1"/>
-      <c r="G34" s="1">
-        <v>0.74913600000000002</v>
-      </c>
-      <c r="H34" s="1">
-        <v>0.75407299999999999</v>
-      </c>
-      <c r="I34" s="1">
-        <v>17.97</v>
-      </c>
-      <c r="K34">
-        <v>0.92</v>
-      </c>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="11" t="s">
-        <v>35</v>
+      <c r="A35" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="B35" s="1">
-        <v>0.73849100000000001</v>
+        <v>0.740506</v>
       </c>
       <c r="C35" s="1">
-        <v>0.86501799999999995</v>
+        <v>0.865591</v>
       </c>
       <c r="D35" s="1">
-        <v>0.827704</v>
+        <v>0.82916100000000004</v>
       </c>
       <c r="E35" s="1"/>
       <c r="F35" s="1">
-        <v>0.74363000000000001</v>
+        <v>0.75195400000000001</v>
       </c>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
-      <c r="I35" s="1" t="s">
-        <v>36</v>
+      <c r="I35" s="1">
+        <v>50.5</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B36" s="1">
-        <v>0.73821400000000004</v>
+        <v>0.73980500000000005</v>
       </c>
       <c r="C36" s="1">
-        <v>0.86428000000000005</v>
+        <v>0.86816499999999996</v>
       </c>
       <c r="D36" s="1">
-        <v>0.82671399999999995</v>
+        <v>0.82677999999999996</v>
       </c>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
@@ -1753,162 +1765,167 @@
       <c r="I36" s="1"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>38</v>
+      <c r="A37" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="B37" s="1">
-        <v>0.73571799999999998</v>
+        <v>0.73975500000000005</v>
       </c>
       <c r="C37" s="1">
-        <v>0.87732399999999999</v>
+        <v>0.85670999999999997</v>
       </c>
       <c r="D37" s="1">
-        <v>0.81230599999999997</v>
-      </c>
-      <c r="E37" s="1"/>
+        <v>0.83675999999999995</v>
+      </c>
+      <c r="E37" s="1">
+        <v>0.74752300000000005</v>
+      </c>
       <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
+      <c r="G37" s="1">
+        <v>0.74913600000000002</v>
+      </c>
+      <c r="H37" s="1">
+        <v>0.75407299999999999</v>
+      </c>
       <c r="I37" s="1">
-        <v>16.73</v>
+        <v>17.97</v>
+      </c>
+      <c r="K37">
+        <v>0.92</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="8" t="s">
-        <v>56</v>
+      <c r="A38" s="11" t="s">
+        <v>35</v>
       </c>
       <c r="B38" s="1">
-        <v>0.73497599999999996</v>
+        <v>0.73849100000000001</v>
       </c>
       <c r="C38" s="1">
-        <v>0.86321599999999998</v>
+        <v>0.86501799999999995</v>
       </c>
       <c r="D38" s="1">
-        <v>0.82403800000000005</v>
+        <v>0.827704</v>
       </c>
       <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1">
-        <v>0.74550499999999997</v>
-      </c>
+      <c r="F38" s="1">
+        <v>0.74363000000000001</v>
+      </c>
+      <c r="G38" s="1"/>
       <c r="H38" s="1"/>
-      <c r="I38" s="1">
-        <v>22.9</v>
+      <c r="I38" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="8" t="s">
-        <v>39</v>
+      <c r="A39" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="B39" s="1">
-        <v>0.73430099999999998</v>
+        <v>0.73821400000000004</v>
       </c>
       <c r="C39" s="1">
-        <v>0.87199099999999996</v>
+        <v>0.86428000000000005</v>
       </c>
       <c r="D39" s="1">
-        <v>0.81632199999999999</v>
+        <v>0.82671399999999995</v>
       </c>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
-      <c r="G39" s="1">
-        <v>0.75073900000000005</v>
-      </c>
+      <c r="G39" s="1"/>
       <c r="H39" s="1"/>
-      <c r="I39" s="1">
-        <v>31</v>
-      </c>
+      <c r="I39" s="1"/>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>40</v>
+      <c r="A40" s="13" t="s">
+        <v>151</v>
       </c>
       <c r="B40" s="1">
-        <v>0.73252300000000004</v>
-      </c>
-      <c r="C40" s="1">
-        <v>0.86758900000000005</v>
-      </c>
-      <c r="D40" s="1">
-        <v>0.81816699999999998</v>
-      </c>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
+        <v>0.73680000000000001</v>
+      </c>
+      <c r="J40">
+        <v>2.65</v>
+      </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B41" s="1">
-        <v>0.73216400000000004</v>
+        <v>0.73571799999999998</v>
       </c>
       <c r="C41" s="1">
-        <v>0.86068100000000003</v>
+        <v>0.87732399999999999</v>
       </c>
       <c r="D41" s="1">
-        <v>0.82388899999999998</v>
+        <v>0.81230599999999997</v>
       </c>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
+      <c r="I41" s="1">
+        <v>16.73</v>
+      </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>42</v>
+      <c r="A42" s="8" t="s">
+        <v>56</v>
       </c>
       <c r="B42" s="1">
-        <v>0.73082899999999995</v>
+        <v>0.73497599999999996</v>
       </c>
       <c r="C42" s="1">
-        <v>0.86943099999999995</v>
+        <v>0.86321599999999998</v>
       </c>
       <c r="D42" s="1">
-        <v>0.81454800000000005</v>
+        <v>0.82403800000000005</v>
       </c>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
+      <c r="G42" s="1">
+        <v>0.74550499999999997</v>
+      </c>
       <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
+      <c r="I42" s="1">
+        <v>22.9</v>
+      </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>43</v>
+      <c r="A43" s="8" t="s">
+        <v>39</v>
       </c>
       <c r="B43" s="1">
-        <v>0.72680400000000001</v>
+        <v>0.73430099999999998</v>
       </c>
       <c r="C43" s="1">
-        <v>0.857101</v>
+        <v>0.87199099999999996</v>
       </c>
       <c r="D43" s="1">
-        <v>0.81938500000000003</v>
+        <v>0.81632199999999999</v>
       </c>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
+      <c r="G43" s="1">
+        <v>0.75073900000000005</v>
+      </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B44" s="1">
-        <v>0.72399400000000003</v>
+        <v>0.73252300000000004</v>
       </c>
       <c r="C44" s="1">
-        <v>0.85761799999999999</v>
+        <v>0.86758900000000005</v>
       </c>
       <c r="D44" s="1">
-        <v>0.81521999999999994</v>
+        <v>0.81816699999999998</v>
       </c>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
@@ -1917,40 +1934,36 @@
       <c r="I44" s="1"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" s="8" t="s">
-        <v>57</v>
+      <c r="A45" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="B45" s="1">
-        <v>0.72123300000000001</v>
+        <v>0.73216400000000004</v>
       </c>
       <c r="C45" s="1">
-        <v>0.85792599999999997</v>
+        <v>0.86068100000000003</v>
       </c>
       <c r="D45" s="1">
-        <v>0.81019799999999997</v>
+        <v>0.82388899999999998</v>
       </c>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
-      <c r="G45" s="1">
-        <v>0.73479399999999995</v>
-      </c>
+      <c r="G45" s="1"/>
       <c r="H45" s="1"/>
-      <c r="I45" s="1">
-        <v>11.42</v>
-      </c>
+      <c r="I45" s="1"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B46" s="1">
-        <v>0.71946500000000002</v>
+        <v>0.73082899999999995</v>
       </c>
       <c r="C46" s="1">
-        <v>0.86807000000000001</v>
+        <v>0.86943099999999995</v>
       </c>
       <c r="D46" s="1">
-        <v>0.80044899999999997</v>
+        <v>0.81454800000000005</v>
       </c>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
@@ -1960,37 +1973,37 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B47" s="1">
-        <v>0.71696099999999996</v>
+        <v>0.72680400000000001</v>
       </c>
       <c r="C47" s="1">
-        <v>0.870251</v>
+        <v>0.857101</v>
       </c>
       <c r="D47" s="1">
-        <v>0.79447199999999996</v>
+        <v>0.81938500000000003</v>
       </c>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
       <c r="I47" s="1">
-        <v>34</v>
+        <v>25</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B48" s="1">
-        <v>0.71694000000000002</v>
+        <v>0.72399400000000003</v>
       </c>
       <c r="C48" s="1">
-        <v>0.86188799999999999</v>
+        <v>0.85761799999999999</v>
       </c>
       <c r="D48" s="1">
-        <v>0.80137999999999998</v>
+        <v>0.81521999999999994</v>
       </c>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
@@ -2000,39 +2013,39 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="B49" s="1">
-        <v>0.71636500000000003</v>
+        <v>0.72123300000000001</v>
       </c>
       <c r="C49" s="1">
-        <v>0.85087000000000002</v>
+        <v>0.85792599999999997</v>
       </c>
       <c r="D49" s="1">
-        <v>0.81111999999999995</v>
+        <v>0.81019799999999997</v>
       </c>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="1">
-        <v>0.73605299999999996</v>
+        <v>0.73479399999999995</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1">
-        <v>7.71</v>
+        <v>11.42</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B50" s="1">
-        <v>0.71354600000000001</v>
+        <v>0.71946500000000002</v>
       </c>
       <c r="C50" s="1">
-        <v>0.869784</v>
+        <v>0.86807000000000001</v>
       </c>
       <c r="D50" s="1">
-        <v>0.79198400000000002</v>
+        <v>0.80044899999999997</v>
       </c>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
@@ -2042,35 +2055,37 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B51" s="1">
-        <v>0.71179099999999995</v>
+        <v>0.71696099999999996</v>
       </c>
       <c r="C51" s="1">
-        <v>0.86646400000000001</v>
+        <v>0.870251</v>
       </c>
       <c r="D51" s="1">
-        <v>0.79112199999999999</v>
+        <v>0.79447199999999996</v>
       </c>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
+      <c r="I51" s="1">
+        <v>34</v>
+      </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B52" s="1">
-        <v>0.711113</v>
+        <v>0.71694000000000002</v>
       </c>
       <c r="C52" s="1">
-        <v>0.84625399999999995</v>
+        <v>0.86188799999999999</v>
       </c>
       <c r="D52" s="1">
-        <v>0.806975</v>
+        <v>0.80137999999999998</v>
       </c>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
@@ -2080,182 +2095,225 @@
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B53" s="1">
-        <v>0.71059899999999998</v>
+        <v>0.71636500000000003</v>
       </c>
       <c r="C53" s="1">
-        <v>0.86808399999999997</v>
+        <v>0.85087000000000002</v>
       </c>
       <c r="D53" s="1">
-        <v>0.78952599999999995</v>
+        <v>0.81111999999999995</v>
       </c>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
       <c r="G53" s="1">
-        <v>0.71683799999999998</v>
+        <v>0.73605299999999996</v>
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="1">
-        <v>25</v>
-      </c>
-      <c r="L53">
-        <v>0.35229700000000003</v>
+        <v>7.71</v>
+      </c>
+      <c r="J53">
+        <v>1.49</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A54" s="8" t="s">
-        <v>53</v>
+      <c r="A54" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="B54" s="1">
-        <v>0.69976499999999997</v>
+        <v>0.71354600000000001</v>
       </c>
       <c r="C54" s="1">
-        <v>0.84911899999999996</v>
+        <v>0.869784</v>
       </c>
       <c r="D54" s="1">
-        <v>0.788358</v>
+        <v>0.79198400000000002</v>
       </c>
       <c r="E54" s="1"/>
-      <c r="F54" s="1">
-        <v>0.69891499999999995</v>
-      </c>
-      <c r="G54" s="1">
-        <v>0.71306599999999998</v>
-      </c>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
       <c r="H54" s="1"/>
-      <c r="I54" s="1">
-        <v>9.74</v>
-      </c>
+      <c r="I54" s="1"/>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A55" s="8" t="s">
-        <v>54</v>
+      <c r="A55" s="13" t="s">
+        <v>149</v>
       </c>
       <c r="B55" s="1">
-        <v>0.69904900000000003</v>
-      </c>
-      <c r="C55" s="1">
-        <v>0.85933199999999998</v>
-      </c>
-      <c r="D55" s="1">
-        <v>0.781447</v>
-      </c>
-      <c r="E55" s="1"/>
-      <c r="F55" s="1"/>
-      <c r="G55" s="1">
-        <v>0.69198599999999999</v>
-      </c>
-      <c r="H55" s="1"/>
-      <c r="I55" s="1">
-        <v>12.94</v>
-      </c>
+        <v>0.71189999999999998</v>
+      </c>
+      <c r="J55">
+        <v>1.33</v>
+      </c>
+      <c r="K55" s="6"/>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B56" s="1">
-        <v>0.69497900000000001</v>
+        <v>0.71179099999999995</v>
       </c>
       <c r="C56" s="1">
-        <v>0.86561600000000005</v>
+        <v>0.86646400000000001</v>
       </c>
       <c r="D56" s="1">
-        <v>0.77168300000000001</v>
+        <v>0.79112199999999999</v>
       </c>
       <c r="E56" s="1"/>
-      <c r="F56" s="1">
-        <v>0.69739899999999999</v>
-      </c>
+      <c r="F56" s="1"/>
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
     </row>
     <row r="57" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="9" t="s">
-        <v>145</v>
+      <c r="A57" s="1" t="s">
+        <v>51</v>
       </c>
       <c r="B57" s="1">
-        <v>0.78243600000000002</v>
+        <v>0.711113</v>
       </c>
       <c r="C57" s="1">
-        <v>0.89274200000000004</v>
+        <v>0.84625399999999995</v>
       </c>
       <c r="D57" s="1">
-        <v>0.85849200000000003</v>
-      </c>
-      <c r="G57" s="1">
-        <v>0.78455699999999995</v>
-      </c>
+        <v>0.806975</v>
+      </c>
+      <c r="J57"/>
+      <c r="K57"/>
+      <c r="L57"/>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A58" s="9" t="s">
-        <v>146</v>
+      <c r="A58" s="8" t="s">
+        <v>52</v>
       </c>
       <c r="B58" s="1">
-        <v>0.78566499999999995</v>
+        <v>0.71059899999999998</v>
       </c>
       <c r="C58" s="1">
-        <v>0.89692000000000005</v>
+        <v>0.86808399999999997</v>
       </c>
       <c r="D58" s="1">
-        <v>0.85882999999999998</v>
-      </c>
-      <c r="G58" s="12">
-        <v>0.79378300000000002</v>
-      </c>
-      <c r="J58">
-        <v>10.67</v>
+        <v>0.78952599999999995</v>
+      </c>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1">
+        <v>0.71683799999999998</v>
+      </c>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1">
+        <v>25</v>
+      </c>
+      <c r="L58">
+        <v>0.35229700000000003</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="B59">
-        <v>0.78639000000000003</v>
-      </c>
-      <c r="C59">
-        <v>0.89660399999999996</v>
-      </c>
-      <c r="D59">
-        <v>0.86029599999999995</v>
+        <v>152</v>
+      </c>
+      <c r="B59" s="1">
+        <v>0.69976499999999997</v>
+      </c>
+      <c r="C59" s="1">
+        <v>0.84911899999999996</v>
+      </c>
+      <c r="D59" s="1">
+        <v>0.788358</v>
+      </c>
+      <c r="E59" s="1"/>
+      <c r="F59" s="1">
+        <v>0.69891499999999995</v>
       </c>
       <c r="G59" s="1">
-        <v>0.78982600000000003</v>
-      </c>
-      <c r="J59">
-        <v>10.33</v>
-      </c>
-      <c r="K59" s="6" t="s">
-        <v>150</v>
+        <v>0.71306599999999998</v>
+      </c>
+      <c r="H59" s="1">
+        <v>0.73507100000000003</v>
+      </c>
+      <c r="I59" s="1">
+        <v>9.74</v>
+      </c>
+      <c r="J59" s="1">
+        <v>1.86</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A60" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="B60">
-        <v>0.71189999999999998</v>
+      <c r="A60" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B60" s="1">
+        <v>0.69904900000000003</v>
+      </c>
+      <c r="C60" s="1">
+        <v>0.85933199999999998</v>
+      </c>
+      <c r="D60" s="1">
+        <v>0.781447</v>
+      </c>
+      <c r="E60" s="1"/>
+      <c r="F60" s="1"/>
+      <c r="G60" s="1">
+        <v>0.69198599999999999</v>
+      </c>
+      <c r="H60" s="1"/>
+      <c r="I60" s="1">
+        <v>12.94</v>
       </c>
       <c r="J60">
-        <v>1.33</v>
-      </c>
-      <c r="K60" s="6"/>
+        <v>2.1</v>
+      </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A61" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="J61">
-        <v>2.65</v>
+      <c r="A61" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B61" s="1">
+        <v>0.69497900000000001</v>
+      </c>
+      <c r="C61" s="1">
+        <v>0.86561600000000005</v>
+      </c>
+      <c r="D61" s="1">
+        <v>0.77168300000000001</v>
+      </c>
+      <c r="E61" s="1"/>
+      <c r="F61" s="1">
+        <v>0.69739899999999999</v>
+      </c>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1"/>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A62" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="H62">
+        <v>0.74091399999999996</v>
+      </c>
+      <c r="J62">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A63" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="H63">
+        <v>0.72148599999999996</v>
+      </c>
+      <c r="J63">
+        <v>1.73</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L58">
-    <sortCondition descending="1" ref="B2:B58"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L61">
+    <sortCondition descending="1" ref="B2:B61"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
